--- a/reports/Debug-purgatory-20260111/For The Day (Actual)_Payroll.xlsx
+++ b/reports/Debug-purgatory-20260111/For The Day (Actual)_Payroll.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1448" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1449" uniqueCount="315">
   <si>
     <t>eecode</t>
   </si>
@@ -22,25 +22,76 @@
     <t>A2TV</t>
   </si>
   <si>
+    <t>A44A</t>
+  </si>
+  <si>
+    <t>A3RS</t>
+  </si>
+  <si>
+    <t>E075</t>
+  </si>
+  <si>
+    <t>A2JG</t>
+  </si>
+  <si>
+    <t>A1B0</t>
+  </si>
+  <si>
+    <t>A0CX</t>
+  </si>
+  <si>
+    <t>B197</t>
+  </si>
+  <si>
+    <t>F683</t>
+  </si>
+  <si>
+    <t>A3JZ</t>
+  </si>
+  <si>
+    <t>J072</t>
+  </si>
+  <si>
+    <t>J399</t>
+  </si>
+  <si>
     <t>A3GJ</t>
   </si>
   <si>
+    <t>A3T7</t>
+  </si>
+  <si>
+    <t>A4AN</t>
+  </si>
+  <si>
     <t>B746</t>
   </si>
   <si>
-    <t>A4AN</t>
-  </si>
-  <si>
-    <t>A3T7</t>
+    <t>A0XN</t>
+  </si>
+  <si>
+    <t>A4CG</t>
+  </si>
+  <si>
+    <t>J520</t>
+  </si>
+  <si>
+    <t>A06T</t>
+  </si>
+  <si>
+    <t>A3DX</t>
+  </si>
+  <si>
+    <t>A3Q0</t>
+  </si>
+  <si>
+    <t>A3RD</t>
   </si>
   <si>
     <t>A3NT</t>
   </si>
   <si>
-    <t>E075</t>
-  </si>
-  <si>
-    <t>B197</t>
+    <t>A3S3</t>
   </si>
   <si>
     <t>A0DO</t>
@@ -52,66 +103,15 @@
     <t>A2JJ</t>
   </si>
   <si>
-    <t>A3S3</t>
-  </si>
-  <si>
-    <t>A3RD</t>
-  </si>
-  <si>
-    <t>A3Q0</t>
-  </si>
-  <si>
-    <t>A3JZ</t>
-  </si>
-  <si>
-    <t>A06T</t>
-  </si>
-  <si>
-    <t>J399</t>
-  </si>
-  <si>
-    <t>A44A</t>
-  </si>
-  <si>
-    <t>A3RS</t>
-  </si>
-  <si>
-    <t>A2JG</t>
-  </si>
-  <si>
-    <t>A1B0</t>
-  </si>
-  <si>
-    <t>A0CX</t>
-  </si>
-  <si>
-    <t>F683</t>
-  </si>
-  <si>
-    <t>A4CG</t>
-  </si>
-  <si>
-    <t>J520</t>
-  </si>
-  <si>
-    <t>A0XN</t>
-  </si>
-  <si>
-    <t>J072</t>
-  </si>
-  <si>
-    <t>A3DX</t>
+    <t>A1JS</t>
+  </si>
+  <si>
+    <t>F406</t>
   </si>
   <si>
     <t>A45A</t>
   </si>
   <si>
-    <t>F406</t>
-  </si>
-  <si>
-    <t>A1JS</t>
-  </si>
-  <si>
     <t>D519</t>
   </si>
   <si>
@@ -121,54 +121,54 @@
     <t>A4HS</t>
   </si>
   <si>
+    <t>A3P7</t>
+  </si>
+  <si>
+    <t>E082</t>
+  </si>
+  <si>
     <t>A449</t>
   </si>
   <si>
-    <t>E082</t>
+    <t>A3SJ</t>
+  </si>
+  <si>
+    <t>D941</t>
+  </si>
+  <si>
+    <t>A3IL</t>
   </si>
   <si>
     <t>A2HF</t>
   </si>
   <si>
-    <t>A3P7</t>
-  </si>
-  <si>
     <t>A1CM</t>
   </si>
   <si>
-    <t>D941</t>
-  </si>
-  <si>
-    <t>A3SJ</t>
-  </si>
-  <si>
-    <t>A3IL</t>
+    <t>A609</t>
   </si>
   <si>
     <t>J056</t>
   </si>
   <si>
-    <t>A609</t>
+    <t>G397</t>
   </si>
   <si>
     <t>F499</t>
   </si>
   <si>
-    <t>G397</t>
+    <t>E135</t>
+  </si>
+  <si>
+    <t>A23C</t>
   </si>
   <si>
     <t>I590</t>
   </si>
   <si>
-    <t>E135</t>
-  </si>
-  <si>
     <t>C653</t>
   </si>
   <si>
-    <t>A23C</t>
-  </si>
-  <si>
     <t>J185</t>
   </si>
   <si>
@@ -181,64 +181,76 @@
     <t>E720</t>
   </si>
   <si>
+    <t>B847</t>
+  </si>
+  <si>
+    <t>B924</t>
+  </si>
+  <si>
+    <t>A2H9</t>
+  </si>
+  <si>
+    <t>D494</t>
+  </si>
+  <si>
+    <t>B898</t>
+  </si>
+  <si>
+    <t>D855</t>
+  </si>
+  <si>
+    <t>J467</t>
+  </si>
+  <si>
+    <t>A3LN</t>
+  </si>
+  <si>
+    <t>A3L3</t>
+  </si>
+  <si>
+    <t>E471</t>
+  </si>
+  <si>
+    <t>A0JI</t>
+  </si>
+  <si>
+    <t>E950</t>
+  </si>
+  <si>
+    <t>I762</t>
+  </si>
+  <si>
     <t>C132</t>
   </si>
   <si>
+    <t>A889</t>
+  </si>
+  <si>
+    <t>H532</t>
+  </si>
+  <si>
+    <t>C208</t>
+  </si>
+  <si>
     <t>J471</t>
   </si>
   <si>
-    <t>B847</t>
-  </si>
-  <si>
-    <t>C208</t>
+    <t>A0JG</t>
   </si>
   <si>
     <t>J442</t>
   </si>
   <si>
-    <t>A0JG</t>
-  </si>
-  <si>
-    <t>J467</t>
-  </si>
-  <si>
-    <t>D494</t>
-  </si>
-  <si>
-    <t>E950</t>
-  </si>
-  <si>
-    <t>A3L3</t>
-  </si>
-  <si>
-    <t>A889</t>
-  </si>
-  <si>
-    <t>B924</t>
-  </si>
-  <si>
-    <t>B898</t>
-  </si>
-  <si>
-    <t>E471</t>
-  </si>
-  <si>
-    <t>A3LN</t>
-  </si>
-  <si>
-    <t>I762</t>
-  </si>
-  <si>
-    <t>A0JI</t>
-  </si>
-  <si>
-    <t>H532</t>
-  </si>
-  <si>
-    <t>A2H9</t>
-  </si>
-  <si>
-    <t>D855</t>
+    <t>A44B</t>
+  </si>
+  <si>
+    <t>A3S8</t>
+  </si>
+  <si>
+    <t>A37N</t>
+  </si>
+  <si>
+    <t>H586</t>
   </si>
   <si>
     <t>A3O1</t>
@@ -247,301 +259,295 @@
     <t>A2Q9</t>
   </si>
   <si>
-    <t>H586</t>
-  </si>
-  <si>
-    <t>A3S8</t>
+    <t>A15K</t>
+  </si>
+  <si>
+    <t>A44D</t>
+  </si>
+  <si>
+    <t>A2O6</t>
+  </si>
+  <si>
+    <t>E547</t>
+  </si>
+  <si>
+    <t>A3NW</t>
+  </si>
+  <si>
+    <t>A2KR</t>
+  </si>
+  <si>
+    <t>A15F</t>
+  </si>
+  <si>
+    <t>A22D</t>
+  </si>
+  <si>
+    <t>A3ZX</t>
+  </si>
+  <si>
+    <t>A45Q</t>
+  </si>
+  <si>
+    <t>D441</t>
+  </si>
+  <si>
+    <t>A3HJ</t>
+  </si>
+  <si>
+    <t>A3G3</t>
+  </si>
+  <si>
+    <t>A1IU</t>
   </si>
   <si>
     <t>A45T</t>
   </si>
   <si>
-    <t>A15K</t>
+    <t>I563</t>
+  </si>
+  <si>
+    <t>A3NY</t>
   </si>
   <si>
     <t>A34H</t>
   </si>
   <si>
-    <t>A15F</t>
-  </si>
-  <si>
-    <t>A22D</t>
-  </si>
-  <si>
-    <t>I563</t>
-  </si>
-  <si>
-    <t>A44B</t>
-  </si>
-  <si>
-    <t>A45Q</t>
-  </si>
-  <si>
-    <t>A44D</t>
-  </si>
-  <si>
-    <t>A2O6</t>
-  </si>
-  <si>
-    <t>A37N</t>
-  </si>
-  <si>
-    <t>A3NY</t>
-  </si>
-  <si>
-    <t>A2KR</t>
-  </si>
-  <si>
-    <t>E547</t>
-  </si>
-  <si>
-    <t>D441</t>
-  </si>
-  <si>
-    <t>A1IU</t>
-  </si>
-  <si>
-    <t>A3G3</t>
-  </si>
-  <si>
-    <t>A3HJ</t>
-  </si>
-  <si>
-    <t>A3ZX</t>
-  </si>
-  <si>
-    <t>A3NW</t>
+    <t>A0FQ</t>
+  </si>
+  <si>
+    <t>A46W</t>
+  </si>
+  <si>
+    <t>A4AZ</t>
+  </si>
+  <si>
+    <t>H209</t>
+  </si>
+  <si>
+    <t>A46U</t>
+  </si>
+  <si>
+    <t>A3RI</t>
+  </si>
+  <si>
+    <t>A3U6</t>
+  </si>
+  <si>
+    <t>A3RZ</t>
+  </si>
+  <si>
+    <t>A3OH</t>
+  </si>
+  <si>
+    <t>A2G2</t>
+  </si>
+  <si>
+    <t>A2D6</t>
+  </si>
+  <si>
+    <t>A3Z4</t>
+  </si>
+  <si>
+    <t>A36Y</t>
+  </si>
+  <si>
+    <t>I452</t>
+  </si>
+  <si>
+    <t>A3JG</t>
+  </si>
+  <si>
+    <t>A3K5</t>
+  </si>
+  <si>
+    <t>A3KK</t>
+  </si>
+  <si>
+    <t>A3L0</t>
+  </si>
+  <si>
+    <t>A3NS</t>
+  </si>
+  <si>
+    <t>A44M</t>
+  </si>
+  <si>
+    <t>A3IO</t>
+  </si>
+  <si>
+    <t>A4FK</t>
+  </si>
+  <si>
+    <t>A29N</t>
+  </si>
+  <si>
+    <t>E587</t>
+  </si>
+  <si>
+    <t>A3J9</t>
   </si>
   <si>
     <t>B741</t>
   </si>
   <si>
-    <t>A0FQ</t>
+    <t>H009</t>
+  </si>
+  <si>
+    <t>A0S2</t>
+  </si>
+  <si>
+    <t>A0QT</t>
+  </si>
+  <si>
+    <t>A29H</t>
+  </si>
+  <si>
+    <t>A2G8</t>
+  </si>
+  <si>
+    <t>A3J7</t>
+  </si>
+  <si>
+    <t>D243</t>
   </si>
   <si>
     <t>A3T1</t>
   </si>
   <si>
-    <t>A0S2</t>
+    <t>A840</t>
+  </si>
+  <si>
+    <t>A1BL</t>
+  </si>
+  <si>
+    <t>A3JE</t>
+  </si>
+  <si>
+    <t>A3KL</t>
+  </si>
+  <si>
+    <t>G931</t>
+  </si>
+  <si>
+    <t>A3VV</t>
+  </si>
+  <si>
+    <t>F007</t>
   </si>
   <si>
     <t>A0FH</t>
   </si>
   <si>
-    <t>H009</t>
-  </si>
-  <si>
-    <t>G931</t>
-  </si>
-  <si>
-    <t>A840</t>
-  </si>
-  <si>
-    <t>A46W</t>
-  </si>
-  <si>
-    <t>A2G2</t>
-  </si>
-  <si>
     <t>A1WX</t>
   </si>
   <si>
-    <t>A36Y</t>
-  </si>
-  <si>
-    <t>A4AZ</t>
-  </si>
-  <si>
-    <t>A3JG</t>
-  </si>
-  <si>
-    <t>A46U</t>
-  </si>
-  <si>
-    <t>H209</t>
-  </si>
-  <si>
-    <t>A0QT</t>
-  </si>
-  <si>
-    <t>A29H</t>
-  </si>
-  <si>
-    <t>A2G8</t>
-  </si>
-  <si>
-    <t>A3J7</t>
-  </si>
-  <si>
-    <t>D243</t>
-  </si>
-  <si>
-    <t>A3L0</t>
-  </si>
-  <si>
-    <t>A3NS</t>
-  </si>
-  <si>
-    <t>A44M</t>
-  </si>
-  <si>
-    <t>F007</t>
-  </si>
-  <si>
-    <t>A3IO</t>
-  </si>
-  <si>
-    <t>A3J9</t>
-  </si>
-  <si>
-    <t>A3U6</t>
-  </si>
-  <si>
-    <t>A3Z4</t>
-  </si>
-  <si>
-    <t>A3RI</t>
-  </si>
-  <si>
-    <t>A3K5</t>
-  </si>
-  <si>
-    <t>A3KK</t>
-  </si>
-  <si>
-    <t>I452</t>
-  </si>
-  <si>
-    <t>A1BL</t>
-  </si>
-  <si>
-    <t>A3RZ</t>
-  </si>
-  <si>
-    <t>A3JE</t>
-  </si>
-  <si>
-    <t>A3VV</t>
-  </si>
-  <si>
-    <t>A4FK</t>
-  </si>
-  <si>
-    <t>E587</t>
-  </si>
-  <si>
-    <t>A29N</t>
-  </si>
-  <si>
-    <t>A2D6</t>
-  </si>
-  <si>
-    <t>A3OH</t>
-  </si>
-  <si>
-    <t>A3KL</t>
-  </si>
-  <si>
     <t>A45U</t>
   </si>
   <si>
     <t>A547</t>
   </si>
   <si>
+    <t>A2AA</t>
+  </si>
+  <si>
+    <t>A0G3</t>
+  </si>
+  <si>
+    <t>A2LP</t>
+  </si>
+  <si>
     <t>I308</t>
   </si>
   <si>
-    <t>A2LP</t>
-  </si>
-  <si>
-    <t>A2AA</t>
-  </si>
-  <si>
-    <t>A0G3</t>
+    <t>A3UA</t>
+  </si>
+  <si>
+    <t>I182</t>
+  </si>
+  <si>
+    <t>A3V5</t>
+  </si>
+  <si>
+    <t>A3VR</t>
+  </si>
+  <si>
+    <t>A3HK</t>
+  </si>
+  <si>
+    <t>A19P</t>
+  </si>
+  <si>
+    <t>A739</t>
   </si>
   <si>
     <t>C789</t>
   </si>
   <si>
-    <t>A3VR</t>
-  </si>
-  <si>
-    <t>A739</t>
-  </si>
-  <si>
-    <t>A3UA</t>
+    <t>B101</t>
   </si>
   <si>
     <t>A4GZ</t>
   </si>
   <si>
-    <t>I182</t>
-  </si>
-  <si>
-    <t>A3V5</t>
-  </si>
-  <si>
-    <t>A19P</t>
-  </si>
-  <si>
-    <t>A3HK</t>
-  </si>
-  <si>
-    <t>B101</t>
-  </si>
-  <si>
     <t>C835</t>
   </si>
   <si>
+    <t>A4G3</t>
+  </si>
+  <si>
+    <t>I704</t>
+  </si>
+  <si>
+    <t>A36T</t>
+  </si>
+  <si>
     <t>A3FO</t>
   </si>
   <si>
-    <t>A4G3</t>
-  </si>
-  <si>
-    <t>I704</t>
-  </si>
-  <si>
-    <t>A36T</t>
+    <t>A3QR</t>
+  </si>
+  <si>
+    <t>J434</t>
+  </si>
+  <si>
+    <t>I518</t>
+  </si>
+  <si>
+    <t>A4D0</t>
+  </si>
+  <si>
+    <t>I517</t>
+  </si>
+  <si>
+    <t>I216</t>
+  </si>
+  <si>
+    <t>A3H7</t>
+  </si>
+  <si>
+    <t>A4BG</t>
+  </si>
+  <si>
+    <t>A2SG</t>
+  </si>
+  <si>
+    <t>A3VO</t>
+  </si>
+  <si>
+    <t>A29V</t>
+  </si>
+  <si>
+    <t>A2WD</t>
   </si>
   <si>
     <t>A3G6</t>
   </si>
   <si>
-    <t>J434</t>
-  </si>
-  <si>
-    <t>I518</t>
-  </si>
-  <si>
-    <t>A4D0</t>
-  </si>
-  <si>
-    <t>A2SG</t>
-  </si>
-  <si>
-    <t>A4BG</t>
-  </si>
-  <si>
-    <t>A29V</t>
-  </si>
-  <si>
-    <t>I517</t>
-  </si>
-  <si>
-    <t>I216</t>
-  </si>
-  <si>
-    <t>A3QR</t>
-  </si>
-  <si>
-    <t>A3VO</t>
-  </si>
-  <si>
-    <t>A2WD</t>
-  </si>
-  <si>
-    <t>A3H7</t>
+    <t>E001</t>
+  </si>
+  <si>
+    <t>A42F</t>
   </si>
   <si>
     <t>A3K9</t>
@@ -568,64 +574,61 @@
     <t>A4BJ</t>
   </si>
   <si>
-    <t>E001</t>
+    <t>A4BI</t>
+  </si>
+  <si>
+    <t>A2HN</t>
+  </si>
+  <si>
+    <t>A3GE</t>
+  </si>
+  <si>
+    <t>A4I2</t>
   </si>
   <si>
     <t>D274</t>
   </si>
   <si>
-    <t>A4I2</t>
-  </si>
-  <si>
-    <t>A3GE</t>
-  </si>
-  <si>
-    <t>A2HN</t>
+    <t>A43Z</t>
+  </si>
+  <si>
+    <t>A15N</t>
   </si>
   <si>
     <t>A0XV</t>
   </si>
   <si>
-    <t>A15N</t>
-  </si>
-  <si>
-    <t>A43Z</t>
-  </si>
-  <si>
-    <t>A4BI</t>
-  </si>
-  <si>
-    <t>A42F</t>
-  </si>
-  <si>
     <t>I666</t>
   </si>
   <si>
+    <t>A4F3</t>
+  </si>
+  <si>
     <t>A3X0</t>
   </si>
   <si>
     <t>A3K4</t>
   </si>
   <si>
-    <t>A4F3</t>
+    <t>D283</t>
   </si>
   <si>
     <t>F313</t>
   </si>
   <si>
-    <t>D283</t>
-  </si>
-  <si>
     <t>A42D</t>
   </si>
   <si>
+    <t>A1N1</t>
+  </si>
+  <si>
+    <t>A3OC</t>
+  </si>
+  <si>
     <t>G314</t>
   </si>
   <si>
-    <t>A1N1</t>
-  </si>
-  <si>
-    <t>A3OC</t>
+    <t>H341</t>
   </si>
   <si>
     <t>A3DT</t>
@@ -634,93 +637,90 @@
     <t>E608</t>
   </si>
   <si>
-    <t>H341</t>
-  </si>
-  <si>
     <t>A3FH</t>
   </si>
   <si>
+    <t>A3HC</t>
+  </si>
+  <si>
     <t>A3HI</t>
   </si>
   <si>
     <t>A2DH</t>
   </si>
   <si>
-    <t>A3HC</t>
-  </si>
-  <si>
     <t>A1BN</t>
   </si>
   <si>
+    <t>E609</t>
+  </si>
+  <si>
     <t>D736</t>
   </si>
   <si>
     <t>A2RO</t>
   </si>
   <si>
+    <t>A0HT</t>
+  </si>
+  <si>
+    <t>A3PE</t>
+  </si>
+  <si>
+    <t>A2UO</t>
+  </si>
+  <si>
+    <t>F518</t>
+  </si>
+  <si>
+    <t>D071</t>
+  </si>
+  <si>
+    <t>A46X</t>
+  </si>
+  <si>
+    <t>A37G</t>
+  </si>
+  <si>
     <t>A2SD</t>
   </si>
   <si>
-    <t>A2UO</t>
-  </si>
-  <si>
     <t>A1WB</t>
   </si>
   <si>
     <t>A0KH</t>
   </si>
   <si>
-    <t>E609</t>
-  </si>
-  <si>
-    <t>A3PE</t>
-  </si>
-  <si>
-    <t>A37G</t>
-  </si>
-  <si>
-    <t>A46X</t>
-  </si>
-  <si>
-    <t>D071</t>
-  </si>
-  <si>
-    <t>F518</t>
-  </si>
-  <si>
-    <t>A0HT</t>
+    <t>D084</t>
+  </si>
+  <si>
+    <t>A3F1</t>
+  </si>
+  <si>
+    <t>A3SY</t>
+  </si>
+  <si>
+    <t>B125</t>
+  </si>
+  <si>
+    <t>A03K</t>
   </si>
   <si>
     <t>A2RJ</t>
   </si>
   <si>
-    <t>A3SY</t>
-  </si>
-  <si>
-    <t>A03K</t>
-  </si>
-  <si>
-    <t>B125</t>
-  </si>
-  <si>
-    <t>A3F1</t>
-  </si>
-  <si>
     <t>F240</t>
   </si>
   <si>
+    <t>A3X1</t>
+  </si>
+  <si>
     <t>F131</t>
   </si>
   <si>
     <t>A2BI</t>
   </si>
   <si>
-    <t>A3X1</t>
-  </si>
-  <si>
-    <t>D084</t>
-  </si>
-  <si>
     <t>F033</t>
   </si>
   <si>
@@ -751,10 +751,10 @@
     <t>ID</t>
   </si>
   <si>
+    <t>HR</t>
+  </si>
+  <si>
     <t>IL</t>
-  </si>
-  <si>
-    <t>HR</t>
   </si>
   <si>
     <t>end_punchtime</t>
@@ -1404,13 +1404,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="2">
-        <v>46033.28813657408</v>
+        <v>46033.37891203703</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D3" s="2">
-        <v>46033.69064814815</v>
+        <v>46033.68344907407</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>249</v>
@@ -1419,7 +1419,7 @@
         <v>252</v>
       </c>
       <c r="G3" s="2">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="H3" s="2">
         <v>0</v>
@@ -1436,13 +1436,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>46033.31</v>
+        <v>46033.31410879629</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D4" s="2">
-        <v>46033.68490740741</v>
+        <v>46033.68283564815</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>249</v>
@@ -1451,7 +1451,7 @@
         <v>252</v>
       </c>
       <c r="G4" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H4" s="2">
         <v>0</v>
@@ -1468,13 +1468,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>46033.30719907407</v>
+        <v>46033.29325231481</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D5" s="2">
-        <v>46033.68708333333</v>
+        <v>46033.68806712963</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>249</v>
@@ -1483,7 +1483,7 @@
         <v>252</v>
       </c>
       <c r="G5" s="2">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="H5" s="2">
         <v>0</v>
@@ -1500,13 +1500,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="2">
-        <v>46033.54252314815</v>
+        <v>46033.30417824074</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D6" s="2">
-        <v>46033.67789351852</v>
+        <v>46033.68305555556</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>249</v>
@@ -1515,7 +1515,7 @@
         <v>252</v>
       </c>
       <c r="G6" s="2">
-        <v>18.5</v>
+        <v>16.25</v>
       </c>
       <c r="H6" s="2">
         <v>0</v>
@@ -1532,13 +1532,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>46033.31738425926</v>
+        <v>46033.29950231482</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D7" s="2">
-        <v>46033.68146990741</v>
+        <v>46033.69006944444</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>249</v>
@@ -1547,7 +1547,7 @@
         <v>252</v>
       </c>
       <c r="G7" s="2">
-        <v>16</v>
+        <v>16.25</v>
       </c>
       <c r="H7" s="2">
         <v>0</v>
@@ -1564,13 +1564,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>46033.29325231481</v>
+        <v>46033.32497685185</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D8" s="2">
-        <v>46033.68806712963</v>
+        <v>46033.68200231482</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>249</v>
@@ -1579,7 +1579,7 @@
         <v>252</v>
       </c>
       <c r="G8" s="2">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="H8" s="2">
         <v>0</v>
@@ -1599,13 +1599,13 @@
         <v>46033.33333333334</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D9" s="2">
         <v>46033.33333333334</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>252</v>
@@ -1628,13 +1628,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="2">
-        <v>46033.28839120371</v>
+        <v>46033.32506944444</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D10" s="2">
-        <v>46033.70550925926</v>
+        <v>46033.68100694445</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>249</v>
@@ -1643,7 +1643,7 @@
         <v>252</v>
       </c>
       <c r="G10" s="2">
-        <v>16.25</v>
+        <v>16.5</v>
       </c>
       <c r="H10" s="2">
         <v>0</v>
@@ -1660,13 +1660,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="2">
-        <v>46033.31179398148</v>
+        <v>46033.33368055556</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D11" s="2">
-        <v>46033.68215277778</v>
+        <v>46033.68116898148</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>249</v>
@@ -1675,7 +1675,7 @@
         <v>252</v>
       </c>
       <c r="G11" s="2">
-        <v>16</v>
+        <v>15.16</v>
       </c>
       <c r="H11" s="2">
         <v>0</v>
@@ -1692,13 +1692,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>46033.30175925926</v>
+        <v>46033.30478009259</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D12" s="2">
-        <v>46033.69409722222</v>
+        <v>46033.67991898148</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>249</v>
@@ -1707,7 +1707,7 @@
         <v>252</v>
       </c>
       <c r="G12" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H12" s="2">
         <v>0</v>
@@ -1724,13 +1724,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>46033.32484953704</v>
+        <v>46033.30677083333</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D13" s="2">
-        <v>46033.70578703703</v>
+        <v>46033.69251157407</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>249</v>
@@ -1739,7 +1739,7 @@
         <v>252</v>
       </c>
       <c r="G13" s="2">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="H13" s="2">
         <v>0</v>
@@ -1756,13 +1756,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>46033.3164699074</v>
+        <v>46033.28813657408</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D14" s="2">
-        <v>46033.68005787037</v>
+        <v>46033.69064814815</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>249</v>
@@ -1771,7 +1771,7 @@
         <v>252</v>
       </c>
       <c r="G14" s="2">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="H14" s="2">
         <v>0</v>
@@ -1788,13 +1788,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="2">
-        <v>46033.30704861111</v>
+        <v>46033.54252314815</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D15" s="2">
-        <v>46033.68467592593</v>
+        <v>46033.67789351852</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>249</v>
@@ -1803,7 +1803,7 @@
         <v>252</v>
       </c>
       <c r="G15" s="2">
-        <v>15.16</v>
+        <v>18.5</v>
       </c>
       <c r="H15" s="2">
         <v>0</v>
@@ -1820,13 +1820,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="2">
-        <v>46033.33368055556</v>
+        <v>46033.30719907407</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D16" s="2">
-        <v>46033.68116898148</v>
+        <v>46033.68708333333</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>249</v>
@@ -1835,7 +1835,7 @@
         <v>252</v>
       </c>
       <c r="G16" s="2">
-        <v>15.16</v>
+        <v>16</v>
       </c>
       <c r="H16" s="2">
         <v>0</v>
@@ -1852,13 +1852,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="2">
-        <v>46033.31206018518</v>
+        <v>46033.31</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D17" s="2">
-        <v>46033.71578703704</v>
+        <v>46033.68490740741</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>249</v>
@@ -1867,7 +1867,7 @@
         <v>252</v>
       </c>
       <c r="G17" s="2">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="H17" s="2">
         <v>0</v>
@@ -1884,13 +1884,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="2">
-        <v>46033.30677083333</v>
+        <v>46033.31582175926</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D18" s="2">
-        <v>46033.69251157407</v>
+        <v>46033.68129629629</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>249</v>
@@ -1899,7 +1899,7 @@
         <v>252</v>
       </c>
       <c r="G18" s="2">
-        <v>16.5</v>
+        <v>16.25</v>
       </c>
       <c r="H18" s="2">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="2">
-        <v>46033.37891203703</v>
+        <v>46033.3019212963</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D19" s="2">
-        <v>46033.68344907407</v>
+        <v>46033.68778935185</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>249</v>
@@ -1948,13 +1948,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="2">
-        <v>46033.31410879629</v>
+        <v>46033.28780092593</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D20" s="2">
-        <v>46033.68283564815</v>
+        <v>46033.7224537037</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>249</v>
@@ -1963,7 +1963,7 @@
         <v>252</v>
       </c>
       <c r="G20" s="2">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="H20" s="2">
         <v>0</v>
@@ -1980,13 +1980,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="2">
-        <v>46033.30417824074</v>
+        <v>46033.31206018518</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D21" s="2">
-        <v>46033.68305555556</v>
+        <v>46033.71578703704</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>249</v>
@@ -1995,7 +1995,7 @@
         <v>252</v>
       </c>
       <c r="G21" s="2">
-        <v>16.25</v>
+        <v>16.5</v>
       </c>
       <c r="H21" s="2">
         <v>0</v>
@@ -2012,13 +2012,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="2">
-        <v>46033.29950231482</v>
+        <v>46033.30143518518</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D22" s="2">
-        <v>46033.69006944444</v>
+        <v>46033.69421296296</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>249</v>
@@ -2027,7 +2027,7 @@
         <v>252</v>
       </c>
       <c r="G22" s="2">
-        <v>16.25</v>
+        <v>16</v>
       </c>
       <c r="H22" s="2">
         <v>0</v>
@@ -2044,13 +2044,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="2">
-        <v>46033.32497685185</v>
+        <v>46033.30704861111</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D23" s="2">
-        <v>46033.68200231482</v>
+        <v>46033.68467592593</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>249</v>
@@ -2059,7 +2059,7 @@
         <v>252</v>
       </c>
       <c r="G23" s="2">
-        <v>15.5</v>
+        <v>15.16</v>
       </c>
       <c r="H23" s="2">
         <v>0</v>
@@ -2076,13 +2076,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="2">
-        <v>46033.32506944444</v>
+        <v>46033.3164699074</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D24" s="2">
-        <v>46033.68100694445</v>
+        <v>46033.68005787037</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>249</v>
@@ -2091,7 +2091,7 @@
         <v>252</v>
       </c>
       <c r="G24" s="2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="H24" s="2">
         <v>0</v>
@@ -2108,13 +2108,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="2">
-        <v>46033.3019212963</v>
+        <v>46033.31738425926</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D25" s="2">
-        <v>46033.68778935185</v>
+        <v>46033.68146990741</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>249</v>
@@ -2140,13 +2140,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="2">
-        <v>46033.28780092593</v>
+        <v>46033.32484953704</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D26" s="2">
-        <v>46033.7224537037</v>
+        <v>46033.70578703703</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>249</v>
@@ -2155,7 +2155,7 @@
         <v>252</v>
       </c>
       <c r="G26" s="2">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="H26" s="2">
         <v>0</v>
@@ -2172,13 +2172,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="2">
-        <v>46033.31582175926</v>
+        <v>46033.28839120371</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D27" s="2">
-        <v>46033.68129629629</v>
+        <v>46033.70550925926</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>249</v>
@@ -2204,13 +2204,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="2">
-        <v>46033.30478009259</v>
+        <v>46033.31179398148</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D28" s="2">
-        <v>46033.67991898148</v>
+        <v>46033.68215277778</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>249</v>
@@ -2236,13 +2236,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="2">
-        <v>46033.30143518518</v>
+        <v>46033.30175925926</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D29" s="2">
-        <v>46033.69421296296</v>
+        <v>46033.69409722222</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>249</v>
@@ -2251,7 +2251,7 @@
         <v>252</v>
       </c>
       <c r="G29" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H29" s="2">
         <v>0</v>
@@ -2268,13 +2268,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="2">
-        <v>46033.26597222222</v>
+        <v>46033.27055555556</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D30" s="2">
-        <v>46033.69783564815</v>
+        <v>46033.68910879629</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>249</v>
@@ -2282,7 +2282,9 @@
       <c r="F30" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="G30" s="2"/>
+      <c r="G30" s="2">
+        <v>26</v>
+      </c>
       <c r="H30" s="2">
         <v>0</v>
       </c>
@@ -2330,13 +2332,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="2">
-        <v>46033.27055555556</v>
+        <v>46033.26597222222</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D32" s="2">
-        <v>46033.68910879629</v>
+        <v>46033.69783564815</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>249</v>
@@ -2344,9 +2346,7 @@
       <c r="F32" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="G32" s="2">
-        <v>26</v>
-      </c>
+      <c r="G32" s="2"/>
       <c r="H32" s="2">
         <v>0</v>
       </c>
@@ -2458,7 +2458,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="2">
-        <v>46033.78870370371</v>
+        <v>46033.79443287037</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>244</v>
@@ -2469,7 +2469,7 @@
         <v>254</v>
       </c>
       <c r="G36" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H36" s="2">
         <v>0</v>
@@ -2514,22 +2514,18 @@
         <v>37</v>
       </c>
       <c r="B38" s="2">
-        <v>46033.31680555556</v>
+        <v>46033.78870370371</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D38" s="2">
-        <v>46033.72916666666</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>249</v>
-      </c>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
       <c r="F38" s="2" t="s">
         <v>254</v>
       </c>
       <c r="G38" s="2">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H38" s="2">
         <v>0</v>
@@ -2546,7 +2542,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="2">
-        <v>46033.79443287037</v>
+        <v>46033.7862037037</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>244</v>
@@ -2557,7 +2553,7 @@
         <v>254</v>
       </c>
       <c r="G39" s="2">
-        <v>21</v>
+        <v>19.1</v>
       </c>
       <c r="H39" s="2">
         <v>0</v>
@@ -2574,18 +2570,22 @@
         <v>39</v>
       </c>
       <c r="B40" s="2">
-        <v>46033.84372685185</v>
+        <v>46033.450625</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
+      <c r="D40" s="2">
+        <v>46034.03946759259</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>249</v>
+      </c>
       <c r="F40" s="2" t="s">
         <v>254</v>
       </c>
       <c r="G40" s="2">
-        <v>19.1</v>
+        <v>23.33</v>
       </c>
       <c r="H40" s="2">
         <v>0</v>
@@ -2599,21 +2599,25 @@
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B41" s="2">
-        <v>46033.37152777778</v>
+        <v>46033.64583333334</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
+      <c r="D41" s="2">
+        <v>46033.78263888889</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>249</v>
+      </c>
       <c r="F41" s="2" t="s">
         <v>254</v>
       </c>
       <c r="G41" s="2">
-        <v>19.1</v>
+        <v>20</v>
       </c>
       <c r="H41" s="2">
         <v>0</v>
@@ -2627,16 +2631,16 @@
     </row>
     <row r="42" spans="1:10">
       <c r="A42" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B42" s="2">
-        <v>46033.450625</v>
+        <v>46033.31680555556</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D42" s="2">
-        <v>46034.03946759259</v>
+        <v>46033.72916666666</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>249</v>
@@ -2645,7 +2649,7 @@
         <v>254</v>
       </c>
       <c r="G42" s="2">
-        <v>23.33</v>
+        <v>20</v>
       </c>
       <c r="H42" s="2">
         <v>0</v>
@@ -2659,10 +2663,10 @@
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B43" s="2">
-        <v>46033.7862037037</v>
+        <v>46033.37152777778</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>244</v>
@@ -2690,22 +2694,18 @@
         <v>42</v>
       </c>
       <c r="B44" s="2">
-        <v>46033.64583333334</v>
+        <v>46033.84372685185</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D44" s="2">
-        <v>46033.78263888889</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>249</v>
-      </c>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
       <c r="F44" s="2" t="s">
         <v>254</v>
       </c>
       <c r="G44" s="2">
-        <v>20</v>
+        <v>19.1</v>
       </c>
       <c r="H44" s="2">
         <v>0</v>
@@ -2722,13 +2722,13 @@
         <v>43</v>
       </c>
       <c r="B45" s="2">
-        <v>46033.319375</v>
+        <v>46033.31782407407</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D45" s="2">
-        <v>46033.73981481481</v>
+        <v>46033.7396875</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>249</v>
@@ -2737,7 +2737,7 @@
         <v>255</v>
       </c>
       <c r="G45" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H45" s="2">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         <v>44</v>
       </c>
       <c r="B46" s="2">
-        <v>46033.31782407407</v>
+        <v>46033.319375</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D46" s="2">
-        <v>46033.7396875</v>
+        <v>46033.73981481481</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>249</v>
@@ -2769,7 +2769,7 @@
         <v>255</v>
       </c>
       <c r="G46" s="2">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H46" s="2">
         <v>0</v>
@@ -2786,13 +2786,13 @@
         <v>45</v>
       </c>
       <c r="B47" s="2">
-        <v>46033.31668981481</v>
+        <v>46033.49283564815</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D47" s="2">
-        <v>46033.73866898148</v>
+        <v>46033.95837962963</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>249</v>
@@ -2801,7 +2801,7 @@
         <v>255</v>
       </c>
       <c r="G47" s="2">
-        <v>19.57</v>
+        <v>22</v>
       </c>
       <c r="H47" s="2">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>46</v>
       </c>
       <c r="B48" s="2">
-        <v>46033.49283564815</v>
+        <v>46033.31668981481</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D48" s="2">
-        <v>46033.95837962963</v>
+        <v>46033.73866898148</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>249</v>
@@ -2833,7 +2833,7 @@
         <v>255</v>
       </c>
       <c r="G48" s="2">
-        <v>22</v>
+        <v>19.57</v>
       </c>
       <c r="H48" s="2">
         <v>0</v>
@@ -2850,13 +2850,13 @@
         <v>47</v>
       </c>
       <c r="B49" s="2">
-        <v>46033.02083333334</v>
+        <v>46033.57729166667</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D49" s="2">
-        <v>46033.4375</v>
+        <v>46034.02423611111</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>249</v>
@@ -2865,7 +2865,7 @@
         <v>256</v>
       </c>
       <c r="G49" s="2">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H49" s="2">
         <v>0</v>
@@ -2882,13 +2882,13 @@
         <v>48</v>
       </c>
       <c r="B50" s="2">
-        <v>46033.57729166667</v>
+        <v>46033.37211805556</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D50" s="2">
-        <v>46034.02423611111</v>
+        <v>46033.84319444445</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>249</v>
@@ -2897,7 +2897,7 @@
         <v>256</v>
       </c>
       <c r="G50" s="2">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="H50" s="2">
         <v>0</v>
@@ -2914,13 +2914,13 @@
         <v>49</v>
       </c>
       <c r="B51" s="2">
-        <v>46033.64550925926</v>
+        <v>46033.02083333334</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D51" s="2">
-        <v>46034.00510416667</v>
+        <v>46033.4375</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>249</v>
@@ -2946,13 +2946,13 @@
         <v>50</v>
       </c>
       <c r="B52" s="2">
-        <v>46033.37211805556</v>
+        <v>46033.64550925926</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D52" s="2">
-        <v>46033.84319444445</v>
+        <v>46034.00510416667</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>249</v>
@@ -2961,7 +2961,7 @@
         <v>256</v>
       </c>
       <c r="G52" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H52" s="2">
         <v>0</v>
@@ -3010,16 +3010,16 @@
         <v>52</v>
       </c>
       <c r="B54" s="2">
-        <v>46033.29008101852</v>
+        <v>46033.52072916667</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D54" s="2">
-        <v>46033.50028935185</v>
+        <v>46033.72983796296</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>257</v>
@@ -3039,25 +3039,25 @@
     </row>
     <row r="55" spans="1:10">
       <c r="A55" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B55" s="2">
-        <v>46033.52072916667</v>
+        <v>46033.2940162037</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D55" s="2">
-        <v>46033.72983796296</v>
+        <v>46033.5517824074</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>257</v>
       </c>
       <c r="G55" s="2">
-        <v>33.14</v>
+        <v>24</v>
       </c>
       <c r="H55" s="2">
         <v>0</v>
@@ -3074,16 +3074,16 @@
         <v>53</v>
       </c>
       <c r="B56" s="2">
-        <v>46033.2940162037</v>
+        <v>46033.55181712963</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D56" s="2">
-        <v>46033.5517824074</v>
+        <v>46033.69092592593</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>257</v>
@@ -3103,25 +3103,25 @@
     </row>
     <row r="57" spans="1:10">
       <c r="A57" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B57" s="2">
-        <v>46033.55181712963</v>
+        <v>46033.29380787037</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D57" s="2">
-        <v>46033.69092592593</v>
+        <v>46033.501875</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>257</v>
       </c>
       <c r="G57" s="2">
-        <v>24</v>
+        <v>26.78</v>
       </c>
       <c r="H57" s="2">
         <v>0</v>
@@ -3138,16 +3138,16 @@
         <v>54</v>
       </c>
       <c r="B58" s="2">
-        <v>46033.29380787037</v>
+        <v>46033.52103009259</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D58" s="2">
-        <v>46033.501875</v>
+        <v>46033.72969907407</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>257</v>
@@ -3167,25 +3167,25 @@
     </row>
     <row r="59" spans="1:10">
       <c r="A59" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B59" s="2">
-        <v>46033.52103009259</v>
+        <v>46033.29008101852</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D59" s="2">
-        <v>46033.72969907407</v>
+        <v>46033.50028935185</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>257</v>
       </c>
       <c r="G59" s="2">
-        <v>26.78</v>
+        <v>33.14</v>
       </c>
       <c r="H59" s="2">
         <v>0</v>
@@ -3202,13 +3202,13 @@
         <v>55</v>
       </c>
       <c r="B60" s="2">
-        <v>46033.31162037037</v>
+        <v>46033.3178125</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D60" s="2">
-        <v>46033.7215162037</v>
+        <v>46033.70621527778</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>249</v>
@@ -3217,7 +3217,7 @@
         <v>258</v>
       </c>
       <c r="G60" s="2">
-        <v>21.72</v>
+        <v>22.58</v>
       </c>
       <c r="H60" s="2">
         <v>0</v>
@@ -3234,13 +3234,13 @@
         <v>56</v>
       </c>
       <c r="B61" s="2">
-        <v>46033.31336805555</v>
+        <v>46033.31364583333</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D61" s="2">
-        <v>46033.68857638889</v>
+        <v>46033.7070949074</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>249</v>
@@ -3249,7 +3249,7 @@
         <v>258</v>
       </c>
       <c r="G61" s="2">
-        <v>24</v>
+        <v>21.22</v>
       </c>
       <c r="H61" s="2">
         <v>0</v>
@@ -3266,13 +3266,13 @@
         <v>57</v>
       </c>
       <c r="B62" s="2">
-        <v>46033.3178125</v>
+        <v>46033.31458333333</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D62" s="2">
-        <v>46033.70621527778</v>
+        <v>46033.70381944445</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>249</v>
@@ -3281,7 +3281,7 @@
         <v>258</v>
       </c>
       <c r="G62" s="2">
-        <v>22.58</v>
+        <v>20.35</v>
       </c>
       <c r="H62" s="2">
         <v>0</v>
@@ -3298,13 +3298,13 @@
         <v>58</v>
       </c>
       <c r="B63" s="2">
-        <v>46033.31326388889</v>
+        <v>46033.31388888889</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D63" s="2">
-        <v>46033.71287037037</v>
+        <v>46033.70689814815</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>249</v>
@@ -3313,7 +3313,7 @@
         <v>258</v>
       </c>
       <c r="G63" s="2">
-        <v>24.08</v>
+        <v>20.35</v>
       </c>
       <c r="H63" s="2">
         <v>0</v>
@@ -3330,13 +3330,13 @@
         <v>59</v>
       </c>
       <c r="B64" s="2">
-        <v>46033.31311342592</v>
+        <v>46033.3184837963</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D64" s="2">
-        <v>46033.70855324074</v>
+        <v>46033.70568287037</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>249</v>
@@ -3345,7 +3345,7 @@
         <v>258</v>
       </c>
       <c r="G64" s="2">
-        <v>27.58</v>
+        <v>26.83</v>
       </c>
       <c r="H64" s="2">
         <v>0</v>
@@ -3362,13 +3362,13 @@
         <v>60</v>
       </c>
       <c r="B65" s="2">
-        <v>46033.31802083334</v>
+        <v>46033.31351851852</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D65" s="2">
-        <v>46033.70824074074</v>
+        <v>46033.71309027778</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>249</v>
@@ -3377,7 +3377,7 @@
         <v>258</v>
       </c>
       <c r="G65" s="2">
-        <v>19.85</v>
+        <v>20.6</v>
       </c>
       <c r="H65" s="2">
         <v>0</v>
@@ -3426,13 +3426,13 @@
         <v>62</v>
       </c>
       <c r="B67" s="2">
-        <v>46033.31388888889</v>
+        <v>46033.31633101852</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D67" s="2">
-        <v>46033.70689814815</v>
+        <v>46033.70186342593</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>249</v>
@@ -3441,7 +3441,7 @@
         <v>258</v>
       </c>
       <c r="G67" s="2">
-        <v>20.35</v>
+        <v>18.03</v>
       </c>
       <c r="H67" s="2">
         <v>0</v>
@@ -3458,13 +3458,13 @@
         <v>63</v>
       </c>
       <c r="B68" s="2">
-        <v>46033.31149305555</v>
+        <v>46033.32012731482</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D68" s="2">
-        <v>46033.7219212963</v>
+        <v>46033.70142361111</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>249</v>
@@ -3473,7 +3473,7 @@
         <v>258</v>
       </c>
       <c r="G68" s="2">
-        <v>19.85</v>
+        <v>19.03</v>
       </c>
       <c r="H68" s="2">
         <v>0</v>
@@ -3490,13 +3490,13 @@
         <v>64</v>
       </c>
       <c r="B69" s="2">
-        <v>46033.32012731482</v>
+        <v>46033.31930555555</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D69" s="2">
-        <v>46033.70142361111</v>
+        <v>46033.70945601852</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>249</v>
@@ -3505,7 +3505,7 @@
         <v>258</v>
       </c>
       <c r="G69" s="2">
-        <v>19.03</v>
+        <v>24.33</v>
       </c>
       <c r="H69" s="2">
         <v>0</v>
@@ -3522,13 +3522,13 @@
         <v>65</v>
       </c>
       <c r="B70" s="2">
-        <v>46033.31285879629</v>
+        <v>46033.3133912037</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D70" s="2">
-        <v>46033.7109375</v>
+        <v>46033.71064814815</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>249</v>
@@ -3554,13 +3554,13 @@
         <v>66</v>
       </c>
       <c r="B71" s="2">
-        <v>46033.31364583333</v>
+        <v>46033.31149305555</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D71" s="2">
-        <v>46033.7070949074</v>
+        <v>46033.7219212963</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>249</v>
@@ -3569,7 +3569,7 @@
         <v>258</v>
       </c>
       <c r="G71" s="2">
-        <v>21.22</v>
+        <v>19.85</v>
       </c>
       <c r="H71" s="2">
         <v>0</v>
@@ -3586,13 +3586,13 @@
         <v>67</v>
       </c>
       <c r="B72" s="2">
-        <v>46033.3184837963</v>
+        <v>46033.31136574074</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D72" s="2">
-        <v>46033.70568287037</v>
+        <v>46033.72171296296</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>249</v>
@@ -3601,7 +3601,7 @@
         <v>258</v>
       </c>
       <c r="G72" s="2">
-        <v>26.83</v>
+        <v>19.85</v>
       </c>
       <c r="H72" s="2">
         <v>0</v>
@@ -3618,13 +3618,13 @@
         <v>68</v>
       </c>
       <c r="B73" s="2">
-        <v>46033.31930555555</v>
+        <v>46033.31162037037</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D73" s="2">
-        <v>46033.70945601852</v>
+        <v>46033.7215162037</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>249</v>
@@ -3633,7 +3633,7 @@
         <v>258</v>
       </c>
       <c r="G73" s="2">
-        <v>24.33</v>
+        <v>21.72</v>
       </c>
       <c r="H73" s="2">
         <v>0</v>
@@ -3650,13 +3650,13 @@
         <v>69</v>
       </c>
       <c r="B74" s="2">
-        <v>46033.31633101852</v>
+        <v>46033.31285879629</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D74" s="2">
-        <v>46033.70186342593</v>
+        <v>46033.7109375</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>249</v>
@@ -3665,7 +3665,7 @@
         <v>258</v>
       </c>
       <c r="G74" s="2">
-        <v>18.03</v>
+        <v>19.85</v>
       </c>
       <c r="H74" s="2">
         <v>0</v>
@@ -3682,13 +3682,13 @@
         <v>70</v>
       </c>
       <c r="B75" s="2">
-        <v>46033.31136574074</v>
+        <v>46033.31827546296</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D75" s="2">
-        <v>46033.72171296296</v>
+        <v>46033.70663194444</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>249</v>
@@ -3714,13 +3714,13 @@
         <v>71</v>
       </c>
       <c r="B76" s="2">
-        <v>46033.3133912037</v>
+        <v>46033.31326388889</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D76" s="2">
-        <v>46033.71064814815</v>
+        <v>46033.71287037037</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>249</v>
@@ -3729,7 +3729,7 @@
         <v>258</v>
       </c>
       <c r="G76" s="2">
-        <v>19.85</v>
+        <v>24.08</v>
       </c>
       <c r="H76" s="2">
         <v>0</v>
@@ -3746,13 +3746,13 @@
         <v>72</v>
       </c>
       <c r="B77" s="2">
-        <v>46033.31827546296</v>
+        <v>46033.31336805555</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D77" s="2">
-        <v>46033.70663194444</v>
+        <v>46033.68857638889</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>249</v>
@@ -3761,7 +3761,7 @@
         <v>258</v>
       </c>
       <c r="G77" s="2">
-        <v>19.85</v>
+        <v>24</v>
       </c>
       <c r="H77" s="2">
         <v>0</v>
@@ -3778,13 +3778,13 @@
         <v>73</v>
       </c>
       <c r="B78" s="2">
-        <v>46033.31458333333</v>
+        <v>46033.31802083334</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D78" s="2">
-        <v>46033.70381944445</v>
+        <v>46033.70824074074</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>249</v>
@@ -3793,7 +3793,7 @@
         <v>258</v>
       </c>
       <c r="G78" s="2">
-        <v>20.35</v>
+        <v>19.85</v>
       </c>
       <c r="H78" s="2">
         <v>0</v>
@@ -3810,13 +3810,13 @@
         <v>74</v>
       </c>
       <c r="B79" s="2">
-        <v>46033.31351851852</v>
+        <v>46033.31311342592</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D79" s="2">
-        <v>46033.71309027778</v>
+        <v>46033.70855324074</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>249</v>
@@ -3825,7 +3825,7 @@
         <v>258</v>
       </c>
       <c r="G79" s="2">
-        <v>20.6</v>
+        <v>27.58</v>
       </c>
       <c r="H79" s="2">
         <v>0</v>
@@ -3842,13 +3842,13 @@
         <v>75</v>
       </c>
       <c r="B80" s="2">
-        <v>46033.33194444444</v>
+        <v>46033.33221064815</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D80" s="2">
-        <v>46033.46112268518</v>
+        <v>46033.41931712963</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>250</v>
@@ -3857,7 +3857,7 @@
         <v>259</v>
       </c>
       <c r="G80" s="2">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="H80" s="2">
         <v>0</v>
@@ -3871,16 +3871,16 @@
     </row>
     <row r="81" spans="1:10">
       <c r="A81" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B81" s="2">
-        <v>46033.50155092592</v>
+        <v>46033.57238425926</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D81" s="2">
-        <v>46033.70796296297</v>
+        <v>46033.70506944445</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>249</v>
@@ -3889,7 +3889,7 @@
         <v>259</v>
       </c>
       <c r="G81" s="2">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="H81" s="2">
         <v>0</v>
@@ -3906,13 +3906,13 @@
         <v>76</v>
       </c>
       <c r="B82" s="2">
-        <v>46033.33019675926</v>
+        <v>46033.33340277777</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D82" s="2">
-        <v>46033.54616898148</v>
+        <v>46033.50560185185</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>250</v>
@@ -3938,22 +3938,22 @@
         <v>77</v>
       </c>
       <c r="B83" s="2">
-        <v>46033.33292824074</v>
+        <v>46033.33384259259</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D83" s="2">
-        <v>46033.5419212963</v>
+        <v>46033.60395833333</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>259</v>
       </c>
       <c r="G83" s="2">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="H83" s="2">
         <v>0</v>
@@ -3970,22 +3970,22 @@
         <v>78</v>
       </c>
       <c r="B84" s="2">
-        <v>46033.57238425926</v>
+        <v>46033.33292824074</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D84" s="2">
-        <v>46033.70506944445</v>
+        <v>46033.5419212963</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>259</v>
       </c>
       <c r="G84" s="2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="H84" s="2">
         <v>0</v>
@@ -3999,25 +3999,25 @@
     </row>
     <row r="85" spans="1:10">
       <c r="A85" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B85" s="2">
-        <v>46033.33340277777</v>
+        <v>46033.50155092592</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D85" s="2">
-        <v>46033.50560185185</v>
+        <v>46033.70796296297</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>259</v>
       </c>
       <c r="G85" s="2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="H85" s="2">
         <v>0</v>
@@ -4034,22 +4034,22 @@
         <v>79</v>
       </c>
       <c r="B86" s="2">
-        <v>46033.33270833334</v>
+        <v>46033.33194444444</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D86" s="2">
-        <v>46033.75118055556</v>
+        <v>46033.46112268518</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>259</v>
       </c>
       <c r="G86" s="2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="H86" s="2">
         <v>0</v>
@@ -4066,22 +4066,22 @@
         <v>80</v>
       </c>
       <c r="B87" s="2">
-        <v>46033.33251157407</v>
+        <v>46033.58293981481</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D87" s="2">
-        <v>46033.42078703704</v>
+        <v>46033.70762731481</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>259</v>
       </c>
       <c r="G87" s="2">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="H87" s="2">
         <v>0</v>
@@ -4095,19 +4095,19 @@
     </row>
     <row r="88" spans="1:10">
       <c r="A88" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B88" s="2">
-        <v>46033.45894675926</v>
+        <v>46033.33251157407</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D88" s="2">
-        <v>46033.70489583333</v>
+        <v>46033.42078703704</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>259</v>
@@ -4127,16 +4127,16 @@
     </row>
     <row r="89" spans="1:10">
       <c r="A89" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B89" s="2">
-        <v>46033.31435185186</v>
+        <v>46033.53611111111</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D89" s="2">
-        <v>46033.56130787037</v>
+        <v>46033.68398148148</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>249</v>
@@ -4145,7 +4145,7 @@
         <v>259</v>
       </c>
       <c r="G89" s="2">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="H89" s="2">
         <v>0</v>
@@ -4159,19 +4159,19 @@
     </row>
     <row r="90" spans="1:10">
       <c r="A90" s="2" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B90" s="2">
-        <v>46033.33107638889</v>
+        <v>46033.4627662037</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D90" s="2">
-        <v>46033.50209490741</v>
+        <v>46033.70528935185</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>259</v>
@@ -4191,25 +4191,25 @@
     </row>
     <row r="91" spans="1:10">
       <c r="A91" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B91" s="2">
-        <v>46033.53655092593</v>
+        <v>46033.33181712963</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D91" s="2">
-        <v>46033.75252314815</v>
+        <v>46033.46231481482</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>259</v>
       </c>
       <c r="G91" s="2">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="H91" s="2">
         <v>0</v>
@@ -4226,22 +4226,22 @@
         <v>83</v>
       </c>
       <c r="B92" s="2">
-        <v>46033.30614583333</v>
+        <v>46033.47778935185</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D92" s="2">
-        <v>46033.52482638889</v>
+        <v>46033.68759259259</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>259</v>
       </c>
       <c r="G92" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H92" s="2">
         <v>0</v>
@@ -4255,16 +4255,16 @@
     </row>
     <row r="93" spans="1:10">
       <c r="A93" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B93" s="2">
-        <v>46033.59368055555</v>
+        <v>46033.32185185186</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D93" s="2">
-        <v>46033.70738425926</v>
+        <v>46033.56490740741</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>249</v>
@@ -4273,7 +4273,7 @@
         <v>259</v>
       </c>
       <c r="G93" s="2">
-        <v>18</v>
+        <v>24.72</v>
       </c>
       <c r="H93" s="2">
         <v>0</v>
@@ -4290,22 +4290,22 @@
         <v>84</v>
       </c>
       <c r="B94" s="2">
-        <v>46033.33353009259</v>
+        <v>46033.5983912037</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D94" s="2">
-        <v>46033.46716435185</v>
+        <v>46033.71266203704</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>259</v>
       </c>
       <c r="G94" s="2">
-        <v>17.5</v>
+        <v>24.72</v>
       </c>
       <c r="H94" s="2">
         <v>0</v>
@@ -4322,13 +4322,13 @@
         <v>85</v>
       </c>
       <c r="B95" s="2">
-        <v>46033.4627662037</v>
+        <v>46033.33788194445</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D95" s="2">
-        <v>46033.70528935185</v>
+        <v>46033.70983796296</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>249</v>
@@ -4337,7 +4337,7 @@
         <v>259</v>
       </c>
       <c r="G95" s="2">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="H95" s="2">
         <v>0</v>
@@ -4351,25 +4351,25 @@
     </row>
     <row r="96" spans="1:10">
       <c r="A96" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B96" s="2">
-        <v>46033.33221064815</v>
+        <v>46033.33153935185</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D96" s="2">
-        <v>46033.41931712963</v>
+        <v>46033.33155092593</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>259</v>
       </c>
       <c r="G96" s="2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="H96" s="2">
         <v>0</v>
@@ -4383,25 +4383,25 @@
     </row>
     <row r="97" spans="1:10">
       <c r="A97" s="2" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="B97" s="2">
-        <v>46033.58293981481</v>
+        <v>46033.33173611111</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D97" s="2">
-        <v>46033.70762731481</v>
+        <v>46033.46223379629</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>259</v>
       </c>
       <c r="G97" s="2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="H97" s="2">
         <v>0</v>
@@ -4418,13 +4418,13 @@
         <v>86</v>
       </c>
       <c r="B98" s="2">
-        <v>46033.48987268518</v>
+        <v>46033.47771990741</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D98" s="2">
-        <v>46033.70276620371</v>
+        <v>46033.68744212963</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>249</v>
@@ -4433,7 +4433,7 @@
         <v>259</v>
       </c>
       <c r="G98" s="2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="H98" s="2">
         <v>0</v>
@@ -4447,19 +4447,19 @@
     </row>
     <row r="99" spans="1:10">
       <c r="A99" s="2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B99" s="2">
-        <v>46033.53611111111</v>
+        <v>46033.33210648148</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D99" s="2">
-        <v>46033.68398148148</v>
+        <v>46033.50171296296</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>259</v>
@@ -4482,13 +4482,13 @@
         <v>87</v>
       </c>
       <c r="B100" s="2">
-        <v>46033.33210648148</v>
+        <v>46033.33107638889</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D100" s="2">
-        <v>46033.50171296296</v>
+        <v>46033.50209490741</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>250</v>
@@ -4511,16 +4511,16 @@
     </row>
     <row r="101" spans="1:10">
       <c r="A101" s="2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="B101" s="2">
-        <v>46033.47778935185</v>
+        <v>46033.45894675926</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D101" s="2">
-        <v>46033.68759259259</v>
+        <v>46033.70489583333</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>249</v>
@@ -4529,7 +4529,7 @@
         <v>259</v>
       </c>
       <c r="G101" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H101" s="2">
         <v>0</v>
@@ -4546,13 +4546,13 @@
         <v>88</v>
       </c>
       <c r="B102" s="2">
-        <v>46033.33181712963</v>
+        <v>46033.30614583333</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D102" s="2">
-        <v>46033.46231481482</v>
+        <v>46033.52482638889</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>250</v>
@@ -4561,7 +4561,7 @@
         <v>259</v>
       </c>
       <c r="G102" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H102" s="2">
         <v>0</v>
@@ -4575,16 +4575,16 @@
     </row>
     <row r="103" spans="1:10">
       <c r="A103" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B103" s="2">
-        <v>46033.33384259259</v>
+        <v>46033.53655092593</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D103" s="2">
-        <v>46033.60395833333</v>
+        <v>46033.75252314815</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>249</v>
@@ -4607,16 +4607,16 @@
     </row>
     <row r="104" spans="1:10">
       <c r="A104" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B104" s="2">
-        <v>46033.49875</v>
+        <v>46033.57770833333</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D104" s="2">
-        <v>46033.71015046296</v>
+        <v>46033.71103009259</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>249</v>
@@ -4625,7 +4625,7 @@
         <v>259</v>
       </c>
       <c r="G104" s="2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="H104" s="2">
         <v>0</v>
@@ -4639,19 +4639,19 @@
     </row>
     <row r="105" spans="1:10">
       <c r="A105" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B105" s="2">
-        <v>46033.50604166667</v>
+        <v>46033.32726851852</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D105" s="2">
-        <v>46033.70869212963</v>
+        <v>46033.4641087963</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>259</v>
@@ -4674,16 +4674,16 @@
         <v>90</v>
       </c>
       <c r="B106" s="2">
-        <v>46033.33399305555</v>
+        <v>46033.48987268518</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D106" s="2">
-        <v>46033.45880787037</v>
+        <v>46033.70276620371</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>259</v>
@@ -4706,13 +4706,13 @@
         <v>91</v>
       </c>
       <c r="B107" s="2">
-        <v>46033.33153935185</v>
+        <v>46033.31946759259</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D107" s="2">
-        <v>46033.33155092593</v>
+        <v>46033.70913194444</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>249</v>
@@ -4721,7 +4721,7 @@
         <v>259</v>
       </c>
       <c r="G107" s="2">
-        <v>18</v>
+        <v>24.72</v>
       </c>
       <c r="H107" s="2">
         <v>0</v>
@@ -4735,16 +4735,16 @@
     </row>
     <row r="108" spans="1:10">
       <c r="A108" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B108" s="2">
-        <v>46033.33173611111</v>
+        <v>46033.33002314815</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D108" s="2">
-        <v>46033.46223379629</v>
+        <v>46033.50050925926</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>250</v>
@@ -4767,16 +4767,16 @@
     </row>
     <row r="109" spans="1:10">
       <c r="A109" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B109" s="2">
-        <v>46033.47771990741</v>
+        <v>46033.5121875</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D109" s="2">
-        <v>46033.68744212963</v>
+        <v>46033.68427083334</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>249</v>
@@ -4785,7 +4785,7 @@
         <v>259</v>
       </c>
       <c r="G109" s="2">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H109" s="2">
         <v>0</v>
@@ -4802,22 +4802,22 @@
         <v>92</v>
       </c>
       <c r="B110" s="2">
-        <v>46033.32185185186</v>
+        <v>46033.26997685185</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D110" s="2">
-        <v>46033.56490740741</v>
+        <v>46033.4865625</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>259</v>
       </c>
       <c r="G110" s="2">
-        <v>24.72</v>
+        <v>24</v>
       </c>
       <c r="H110" s="2">
         <v>0</v>
@@ -4834,13 +4834,13 @@
         <v>93</v>
       </c>
       <c r="B111" s="2">
-        <v>46033.31946759259</v>
+        <v>46033.62136574074</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D111" s="2">
-        <v>46033.70913194444</v>
+        <v>46033.70282407408</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>249</v>
@@ -4849,7 +4849,7 @@
         <v>259</v>
       </c>
       <c r="G111" s="2">
-        <v>24.72</v>
+        <v>17.5</v>
       </c>
       <c r="H111" s="2">
         <v>0</v>
@@ -4863,16 +4863,16 @@
     </row>
     <row r="112" spans="1:10">
       <c r="A112" s="2" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="B112" s="2">
-        <v>46033.340625</v>
+        <v>46033.33019675926</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D112" s="2">
-        <v>46033.5418287037</v>
+        <v>46033.54616898148</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>250</v>
@@ -4901,7 +4901,7 @@
         <v>46033.57954861111</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D113" s="2">
         <v>46033.70847222222</v>
@@ -4927,16 +4927,16 @@
     </row>
     <row r="114" spans="1:10">
       <c r="A114" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B114" s="2">
-        <v>46033.32940972222</v>
+        <v>46033.340625</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D114" s="2">
-        <v>46033.54086805556</v>
+        <v>46033.5418287037</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>250</v>
@@ -4962,13 +4962,13 @@
         <v>95</v>
       </c>
       <c r="B115" s="2">
-        <v>46033.62136574074</v>
+        <v>46033.33270833334</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D115" s="2">
-        <v>46033.70282407408</v>
+        <v>46033.75118055556</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>249</v>
@@ -4994,22 +4994,22 @@
         <v>96</v>
       </c>
       <c r="B116" s="2">
-        <v>46033.26997685185</v>
+        <v>46033.50604166667</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D116" s="2">
-        <v>46033.4865625</v>
+        <v>46033.70869212963</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>259</v>
       </c>
       <c r="G116" s="2">
-        <v>24</v>
+        <v>17.5</v>
       </c>
       <c r="H116" s="2">
         <v>0</v>
@@ -5026,22 +5026,22 @@
         <v>96</v>
       </c>
       <c r="B117" s="2">
-        <v>46033.5121875</v>
+        <v>46033.33353009259</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D117" s="2">
-        <v>46033.68427083334</v>
+        <v>46033.46716435185</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>259</v>
       </c>
       <c r="G117" s="2">
-        <v>24</v>
+        <v>17.5</v>
       </c>
       <c r="H117" s="2">
         <v>0</v>
@@ -5058,22 +5058,22 @@
         <v>97</v>
       </c>
       <c r="B118" s="2">
-        <v>46033.33002314815</v>
+        <v>46033.49875</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D118" s="2">
-        <v>46033.50050925926</v>
+        <v>46033.71015046296</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>259</v>
       </c>
       <c r="G118" s="2">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="H118" s="2">
         <v>0</v>
@@ -5090,22 +5090,22 @@
         <v>97</v>
       </c>
       <c r="B119" s="2">
-        <v>46033.57770833333</v>
+        <v>46033.33399305555</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D119" s="2">
-        <v>46033.71103009259</v>
+        <v>46033.45880787037</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>259</v>
       </c>
       <c r="G119" s="2">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="H119" s="2">
         <v>0</v>
@@ -5119,25 +5119,25 @@
     </row>
     <row r="120" spans="1:10">
       <c r="A120" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="B120" s="2">
-        <v>46033.32726851852</v>
+        <v>46033.31435185186</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D120" s="2">
-        <v>46033.4641087963</v>
+        <v>46033.56130787037</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>259</v>
       </c>
       <c r="G120" s="2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="H120" s="2">
         <v>0</v>
@@ -5151,25 +5151,25 @@
     </row>
     <row r="121" spans="1:10">
       <c r="A121" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B121" s="2">
-        <v>46033.5983912037</v>
+        <v>46033.32940972222</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D121" s="2">
-        <v>46033.71266203704</v>
+        <v>46033.54086805556</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>259</v>
       </c>
       <c r="G121" s="2">
-        <v>24.72</v>
+        <v>17.5</v>
       </c>
       <c r="H121" s="2">
         <v>0</v>
@@ -5183,16 +5183,16 @@
     </row>
     <row r="122" spans="1:10">
       <c r="A122" s="2" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B122" s="2">
-        <v>46033.33788194445</v>
+        <v>46033.59368055555</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D122" s="2">
-        <v>46033.70983796296</v>
+        <v>46033.70738425926</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>249</v>
@@ -5201,7 +5201,7 @@
         <v>259</v>
       </c>
       <c r="G122" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H122" s="2">
         <v>0</v>
@@ -5221,25 +5221,25 @@
         <v>46033</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D123" s="2">
         <v>46033</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>260</v>
       </c>
       <c r="G123" s="2">
-        <v>15.5</v>
+        <v>16.67</v>
       </c>
       <c r="H123" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I123" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J123" s="2" t="s">
         <v>294</v>
@@ -5253,19 +5253,19 @@
         <v>46033</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D124" s="2">
         <v>46033</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>260</v>
       </c>
       <c r="G124" s="2">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="H124" s="2">
         <v>6</v>
@@ -5285,19 +5285,19 @@
         <v>46033</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D125" s="2">
         <v>46033</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>260</v>
       </c>
       <c r="G125" s="2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="H125" s="2">
         <v>6</v>
@@ -5317,22 +5317,22 @@
         <v>46033</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D126" s="2">
         <v>46033</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F126" s="2" t="s">
         <v>260</v>
       </c>
       <c r="G126" s="2">
-        <v>19.24</v>
+        <v>17.43</v>
       </c>
       <c r="H126" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I126" s="2">
         <v>0</v>
@@ -5349,22 +5349,22 @@
         <v>46033</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D127" s="2">
         <v>46033</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>260</v>
       </c>
       <c r="G127" s="2">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="H127" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I127" s="2">
         <v>0</v>
@@ -5378,25 +5378,25 @@
         <v>104</v>
       </c>
       <c r="B128" s="2">
-        <v>46033</v>
+        <v>46033.49980324074</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D128" s="2">
-        <v>46033</v>
+        <v>46033.80396990741</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="F128" s="2" t="s">
         <v>260</v>
       </c>
       <c r="G128" s="2">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="H128" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I128" s="2">
         <v>0</v>
@@ -5410,25 +5410,25 @@
         <v>105</v>
       </c>
       <c r="B129" s="2">
-        <v>46033.33700231482</v>
+        <v>46033</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D129" s="2">
-        <v>46033.69409722222</v>
+        <v>46033</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="F129" s="2" t="s">
         <v>260</v>
       </c>
       <c r="G129" s="2">
-        <v>18.2</v>
+        <v>15.5</v>
       </c>
       <c r="H129" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I129" s="2">
         <v>0</v>
@@ -5445,22 +5445,22 @@
         <v>46033</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D130" s="2">
         <v>46033</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F130" s="2" t="s">
         <v>260</v>
       </c>
       <c r="G130" s="2">
-        <v>18.3</v>
+        <v>15.5</v>
       </c>
       <c r="H130" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I130" s="2">
         <v>0</v>
@@ -5471,19 +5471,19 @@
     </row>
     <row r="131" spans="1:10">
       <c r="A131" s="2" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="B131" s="2">
         <v>46033</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D131" s="2">
         <v>46033</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>260</v>
@@ -5492,10 +5492,10 @@
         <v>16</v>
       </c>
       <c r="H131" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I131" s="2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J131" s="2" t="s">
         <v>294</v>
@@ -5503,25 +5503,25 @@
     </row>
     <row r="132" spans="1:10">
       <c r="A132" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B132" s="2">
         <v>46033</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D132" s="2">
         <v>46033</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>260</v>
       </c>
       <c r="G132" s="2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="H132" s="2">
         <v>6</v>
@@ -5535,25 +5535,25 @@
     </row>
     <row r="133" spans="1:10">
       <c r="A133" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B133" s="2">
         <v>46033</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D133" s="2">
         <v>46033</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>260</v>
       </c>
       <c r="G133" s="2">
-        <v>15.5</v>
+        <v>30</v>
       </c>
       <c r="H133" s="2">
         <v>6</v>
@@ -5567,25 +5567,25 @@
     </row>
     <row r="134" spans="1:10">
       <c r="A134" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B134" s="2">
         <v>46033</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D134" s="2">
         <v>46033</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>260</v>
       </c>
       <c r="G134" s="2">
-        <v>17.64</v>
+        <v>15.5</v>
       </c>
       <c r="H134" s="2">
         <v>6</v>
@@ -5599,19 +5599,19 @@
     </row>
     <row r="135" spans="1:10">
       <c r="A135" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B135" s="2">
         <v>46033</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D135" s="2">
         <v>46033</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>260</v>
@@ -5631,28 +5631,28 @@
     </row>
     <row r="136" spans="1:10">
       <c r="A136" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B136" s="2">
         <v>46033</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D136" s="2">
         <v>46033</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>260</v>
       </c>
       <c r="G136" s="2">
-        <v>15.5</v>
+        <v>18.13</v>
       </c>
       <c r="H136" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I136" s="2">
         <v>0</v>
@@ -5663,19 +5663,19 @@
     </row>
     <row r="137" spans="1:10">
       <c r="A137" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B137" s="2">
         <v>46033</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D137" s="2">
         <v>46033</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F137" s="2" t="s">
         <v>260</v>
@@ -5701,25 +5701,25 @@
         <v>46033</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D138" s="2">
         <v>46033</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>260</v>
       </c>
       <c r="G138" s="2">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="H138" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I138" s="2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J138" s="2" t="s">
         <v>294</v>
@@ -5733,19 +5733,19 @@
         <v>46033</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D139" s="2">
         <v>46033</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F139" s="2" t="s">
         <v>260</v>
       </c>
       <c r="G139" s="2">
-        <v>17.43</v>
+        <v>15.5</v>
       </c>
       <c r="H139" s="2">
         <v>6</v>
@@ -5765,19 +5765,19 @@
         <v>46033</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D140" s="2">
         <v>46033</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F140" s="2" t="s">
         <v>260</v>
       </c>
       <c r="G140" s="2">
-        <v>17.8</v>
+        <v>16</v>
       </c>
       <c r="H140" s="2">
         <v>6</v>
@@ -5797,22 +5797,22 @@
         <v>46033</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D141" s="2">
         <v>46033</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F141" s="2" t="s">
         <v>260</v>
       </c>
       <c r="G141" s="2">
-        <v>16.64</v>
+        <v>16</v>
       </c>
       <c r="H141" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I141" s="2">
         <v>0</v>
@@ -5823,31 +5823,31 @@
     </row>
     <row r="142" spans="1:10">
       <c r="A142" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B142" s="2">
         <v>46033</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D142" s="2">
         <v>46033</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F142" s="2" t="s">
         <v>260</v>
       </c>
       <c r="G142" s="2">
-        <v>16.64</v>
+        <v>15.5</v>
       </c>
       <c r="H142" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I142" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J142" s="2" t="s">
         <v>294</v>
@@ -5855,28 +5855,28 @@
     </row>
     <row r="143" spans="1:10">
       <c r="A143" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B143" s="2">
         <v>46033</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D143" s="2">
         <v>46033</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F143" s="2" t="s">
         <v>260</v>
       </c>
       <c r="G143" s="2">
-        <v>30</v>
+        <v>15.5</v>
       </c>
       <c r="H143" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I143" s="2">
         <v>0</v>
@@ -5887,31 +5887,31 @@
     </row>
     <row r="144" spans="1:10">
       <c r="A144" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B144" s="2">
         <v>46033</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D144" s="2">
         <v>46033</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F144" s="2" t="s">
         <v>260</v>
       </c>
       <c r="G144" s="2">
-        <v>30</v>
+        <v>15.5</v>
       </c>
       <c r="H144" s="2">
         <v>0</v>
       </c>
       <c r="I144" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J144" s="2" t="s">
         <v>294</v>
@@ -5919,25 +5919,25 @@
     </row>
     <row r="145" spans="1:10">
       <c r="A145" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B145" s="2">
         <v>46033</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D145" s="2">
         <v>46033</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F145" s="2" t="s">
         <v>260</v>
       </c>
       <c r="G145" s="2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="H145" s="2">
         <v>6</v>
@@ -5951,28 +5951,28 @@
     </row>
     <row r="146" spans="1:10">
       <c r="A146" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B146" s="2">
         <v>46033</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D146" s="2">
         <v>46033</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F146" s="2" t="s">
         <v>260</v>
       </c>
       <c r="G146" s="2">
-        <v>23.28</v>
+        <v>15.5</v>
       </c>
       <c r="H146" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I146" s="2">
         <v>0</v>
@@ -5983,28 +5983,28 @@
     </row>
     <row r="147" spans="1:10">
       <c r="A147" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B147" s="2">
         <v>46033</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D147" s="2">
         <v>46033</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F147" s="2" t="s">
         <v>260</v>
       </c>
       <c r="G147" s="2">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="H147" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I147" s="2">
         <v>0</v>
@@ -6015,28 +6015,28 @@
     </row>
     <row r="148" spans="1:10">
       <c r="A148" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B148" s="2">
         <v>46033</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D148" s="2">
         <v>46033</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F148" s="2" t="s">
         <v>260</v>
       </c>
       <c r="G148" s="2">
-        <v>15.5</v>
+        <v>19.15</v>
       </c>
       <c r="H148" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I148" s="2">
         <v>0</v>
@@ -6047,19 +6047,19 @@
     </row>
     <row r="149" spans="1:10">
       <c r="A149" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B149" s="2">
         <v>46033</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D149" s="2">
         <v>46033</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F149" s="2" t="s">
         <v>260</v>
@@ -6068,7 +6068,7 @@
         <v>15.5</v>
       </c>
       <c r="H149" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I149" s="2">
         <v>0</v>
@@ -6079,19 +6079,19 @@
     </row>
     <row r="150" spans="1:10">
       <c r="A150" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B150" s="2">
         <v>46033</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D150" s="2">
         <v>46033</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F150" s="2" t="s">
         <v>260</v>
@@ -6111,28 +6111,28 @@
     </row>
     <row r="151" spans="1:10">
       <c r="A151" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B151" s="2">
         <v>46033</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D151" s="2">
         <v>46033</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F151" s="2" t="s">
         <v>260</v>
       </c>
       <c r="G151" s="2">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="H151" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I151" s="2">
         <v>0</v>
@@ -6143,28 +6143,28 @@
     </row>
     <row r="152" spans="1:10">
       <c r="A152" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B152" s="2">
         <v>46033</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D152" s="2">
         <v>46033</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F152" s="2" t="s">
         <v>260</v>
       </c>
       <c r="G152" s="2">
-        <v>16</v>
+        <v>19.24</v>
       </c>
       <c r="H152" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I152" s="2">
         <v>0</v>
@@ -6175,25 +6175,25 @@
     </row>
     <row r="153" spans="1:10">
       <c r="A153" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B153" s="2">
         <v>46033</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D153" s="2">
         <v>46033</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F153" s="2" t="s">
         <v>260</v>
       </c>
       <c r="G153" s="2">
-        <v>15.5</v>
+        <v>17.8</v>
       </c>
       <c r="H153" s="2">
         <v>6</v>
@@ -6207,28 +6207,28 @@
     </row>
     <row r="154" spans="1:10">
       <c r="A154" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B154" s="2">
         <v>46033</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D154" s="2">
         <v>46033</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F154" s="2" t="s">
         <v>260</v>
       </c>
       <c r="G154" s="2">
-        <v>15.5</v>
+        <v>16.64</v>
       </c>
       <c r="H154" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I154" s="2">
         <v>0</v>
@@ -6239,31 +6239,31 @@
     </row>
     <row r="155" spans="1:10">
       <c r="A155" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B155" s="2">
         <v>46033</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D155" s="2">
         <v>46033</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F155" s="2" t="s">
         <v>260</v>
       </c>
       <c r="G155" s="2">
-        <v>15.5</v>
+        <v>16.64</v>
       </c>
       <c r="H155" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I155" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J155" s="2" t="s">
         <v>294</v>
@@ -6271,28 +6271,28 @@
     </row>
     <row r="156" spans="1:10">
       <c r="A156" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B156" s="2">
-        <v>46033.49980324074</v>
+        <v>46033</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D156" s="2">
-        <v>46033.80396990741</v>
+        <v>46033</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="F156" s="2" t="s">
         <v>260</v>
       </c>
       <c r="G156" s="2">
-        <v>15.5</v>
+        <v>30</v>
       </c>
       <c r="H156" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I156" s="2">
         <v>0</v>
@@ -6303,31 +6303,31 @@
     </row>
     <row r="157" spans="1:10">
       <c r="A157" s="2" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="B157" s="2">
         <v>46033</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D157" s="2">
         <v>46033</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F157" s="2" t="s">
         <v>260</v>
       </c>
       <c r="G157" s="2">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="H157" s="2">
         <v>0</v>
       </c>
       <c r="I157" s="2">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J157" s="2" t="s">
         <v>294</v>
@@ -6335,19 +6335,19 @@
     </row>
     <row r="158" spans="1:10">
       <c r="A158" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B158" s="2">
         <v>46033</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D158" s="2">
         <v>46033</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F158" s="2" t="s">
         <v>260</v>
@@ -6367,25 +6367,25 @@
     </row>
     <row r="159" spans="1:10">
       <c r="A159" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B159" s="2">
         <v>46033</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D159" s="2">
         <v>46033</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F159" s="2" t="s">
         <v>260</v>
       </c>
       <c r="G159" s="2">
-        <v>16</v>
+        <v>23.28</v>
       </c>
       <c r="H159" s="2">
         <v>6</v>
@@ -6399,28 +6399,28 @@
     </row>
     <row r="160" spans="1:10">
       <c r="A160" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B160" s="2">
         <v>46033</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D160" s="2">
         <v>46033</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F160" s="2" t="s">
         <v>260</v>
       </c>
       <c r="G160" s="2">
-        <v>18.13</v>
+        <v>16</v>
       </c>
       <c r="H160" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I160" s="2">
         <v>0</v>
@@ -6431,28 +6431,28 @@
     </row>
     <row r="161" spans="1:10">
       <c r="A161" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B161" s="2">
         <v>46033</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D161" s="2">
         <v>46033</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F161" s="2" t="s">
         <v>260</v>
       </c>
       <c r="G161" s="2">
-        <v>15.5</v>
+        <v>18.3</v>
       </c>
       <c r="H161" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I161" s="2">
         <v>0</v>
@@ -6469,25 +6469,25 @@
         <v>46033</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D162" s="2">
         <v>46033</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F162" s="2" t="s">
         <v>260</v>
       </c>
       <c r="G162" s="2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="H162" s="2">
         <v>0</v>
       </c>
       <c r="I162" s="2">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J162" s="2" t="s">
         <v>294</v>
@@ -6495,19 +6495,19 @@
     </row>
     <row r="163" spans="1:10">
       <c r="A163" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B163" s="2">
         <v>46033</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D163" s="2">
         <v>46033</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F163" s="2" t="s">
         <v>260</v>
@@ -6516,10 +6516,10 @@
         <v>15.5</v>
       </c>
       <c r="H163" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I163" s="2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J163" s="2" t="s">
         <v>294</v>
@@ -6527,19 +6527,19 @@
     </row>
     <row r="164" spans="1:10">
       <c r="A164" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B164" s="2">
         <v>46033</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D164" s="2">
         <v>46033</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F164" s="2" t="s">
         <v>260</v>
@@ -6548,10 +6548,10 @@
         <v>16</v>
       </c>
       <c r="H164" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I164" s="2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J164" s="2" t="s">
         <v>294</v>
@@ -6559,19 +6559,19 @@
     </row>
     <row r="165" spans="1:10">
       <c r="A165" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B165" s="2">
         <v>46033</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D165" s="2">
         <v>46033</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F165" s="2" t="s">
         <v>260</v>
@@ -6580,10 +6580,10 @@
         <v>16</v>
       </c>
       <c r="H165" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I165" s="2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J165" s="2" t="s">
         <v>294</v>
@@ -6591,19 +6591,19 @@
     </row>
     <row r="166" spans="1:10">
       <c r="A166" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B166" s="2">
         <v>46033</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D166" s="2">
         <v>46033</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F166" s="2" t="s">
         <v>260</v>
@@ -6623,28 +6623,28 @@
     </row>
     <row r="167" spans="1:10">
       <c r="A167" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B167" s="2">
-        <v>46033</v>
+        <v>46033.33700231482</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D167" s="2">
-        <v>46033</v>
+        <v>46033.69409722222</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="F167" s="2" t="s">
         <v>260</v>
       </c>
       <c r="G167" s="2">
-        <v>15.5</v>
+        <v>18.2</v>
       </c>
       <c r="H167" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I167" s="2">
         <v>0</v>
@@ -6655,28 +6655,28 @@
     </row>
     <row r="168" spans="1:10">
       <c r="A168" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B168" s="2">
         <v>46033</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D168" s="2">
         <v>46033</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F168" s="2" t="s">
         <v>260</v>
       </c>
       <c r="G168" s="2">
-        <v>19.15</v>
+        <v>15.5</v>
       </c>
       <c r="H168" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I168" s="2">
         <v>0</v>
@@ -6687,28 +6687,28 @@
     </row>
     <row r="169" spans="1:10">
       <c r="A169" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B169" s="2">
         <v>46033</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D169" s="2">
         <v>46033</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F169" s="2" t="s">
         <v>260</v>
       </c>
       <c r="G169" s="2">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="H169" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I169" s="2">
         <v>0</v>
@@ -6719,25 +6719,25 @@
     </row>
     <row r="170" spans="1:10">
       <c r="A170" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B170" s="2">
         <v>46033</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D170" s="2">
         <v>46033</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F170" s="2" t="s">
         <v>260</v>
       </c>
       <c r="G170" s="2">
-        <v>30</v>
+        <v>15.5</v>
       </c>
       <c r="H170" s="2">
         <v>6</v>
@@ -6751,28 +6751,28 @@
     </row>
     <row r="171" spans="1:10">
       <c r="A171" s="2" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B171" s="2">
         <v>46033</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D171" s="2">
         <v>46033</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F171" s="2" t="s">
         <v>260</v>
       </c>
       <c r="G171" s="2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="H171" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I171" s="2">
         <v>0</v>
@@ -6789,19 +6789,19 @@
         <v>46033</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D172" s="2">
         <v>46033</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F172" s="2" t="s">
         <v>260</v>
       </c>
       <c r="G172" s="2">
-        <v>15.5</v>
+        <v>17.64</v>
       </c>
       <c r="H172" s="2">
         <v>6</v>
@@ -6847,13 +6847,13 @@
     </row>
     <row r="174" spans="1:10">
       <c r="A174" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B174" s="2">
         <v>46033.58297453704</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D174" s="2">
         <v>46033.7096875</v>
@@ -6914,13 +6914,13 @@
         <v>144</v>
       </c>
       <c r="B176" s="2">
-        <v>46033.33605324074</v>
+        <v>46033.57575231481</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D176" s="2">
-        <v>46033.69546296296</v>
+        <v>46033.69646990741</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>249</v>
@@ -6929,7 +6929,7 @@
         <v>264</v>
       </c>
       <c r="G176" s="2">
-        <v>12.14</v>
+        <v>15.16</v>
       </c>
       <c r="H176" s="2">
         <v>0</v>
@@ -6946,22 +6946,18 @@
         <v>145</v>
       </c>
       <c r="B177" s="2">
-        <v>46033.34927083334</v>
+        <v>46033.33813657407</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D177" s="2">
-        <v>46033.54023148148</v>
-      </c>
-      <c r="E177" s="2" t="s">
-        <v>250</v>
-      </c>
+      <c r="D177" s="2"/>
+      <c r="E177" s="2"/>
       <c r="F177" s="2" t="s">
         <v>264</v>
       </c>
       <c r="G177" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H177" s="2">
         <v>0</v>
@@ -6975,25 +6971,25 @@
     </row>
     <row r="178" spans="1:10">
       <c r="A178" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B178" s="2">
-        <v>46033.56561342593</v>
+        <v>46033.33378472222</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D178" s="2">
-        <v>46033.69439814815</v>
+        <v>46033.54064814815</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F178" s="2" t="s">
         <v>264</v>
       </c>
       <c r="G178" s="2">
-        <v>18</v>
+        <v>15.16</v>
       </c>
       <c r="H178" s="2">
         <v>0</v>
@@ -7010,22 +7006,22 @@
         <v>146</v>
       </c>
       <c r="B179" s="2">
-        <v>46033.33378472222</v>
+        <v>46033.56561342593</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D179" s="2">
-        <v>46033.54064814815</v>
+        <v>46033.69439814815</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F179" s="2" t="s">
         <v>264</v>
       </c>
       <c r="G179" s="2">
-        <v>15.16</v>
+        <v>18</v>
       </c>
       <c r="H179" s="2">
         <v>0</v>
@@ -7042,18 +7038,22 @@
         <v>147</v>
       </c>
       <c r="B180" s="2">
-        <v>46033.33813657407</v>
+        <v>46033.33605324074</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D180" s="2"/>
-      <c r="E180" s="2"/>
+      <c r="D180" s="2">
+        <v>46033.69546296296</v>
+      </c>
+      <c r="E180" s="2" t="s">
+        <v>249</v>
+      </c>
       <c r="F180" s="2" t="s">
         <v>264</v>
       </c>
       <c r="G180" s="2">
-        <v>19</v>
+        <v>12.14</v>
       </c>
       <c r="H180" s="2">
         <v>0</v>
@@ -7070,22 +7070,22 @@
         <v>146</v>
       </c>
       <c r="B181" s="2">
-        <v>46033.57575231481</v>
+        <v>46033.34927083334</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D181" s="2">
-        <v>46033.69646990741</v>
+        <v>46033.54023148148</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F181" s="2" t="s">
         <v>264</v>
       </c>
       <c r="G181" s="2">
-        <v>15.16</v>
+        <v>18</v>
       </c>
       <c r="H181" s="2">
         <v>0</v>
@@ -7102,13 +7102,13 @@
         <v>148</v>
       </c>
       <c r="B182" s="2">
-        <v>46033.3380787037</v>
+        <v>46033.33432870371</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D182" s="2">
-        <v>46033.6534375</v>
+        <v>46033.6796412037</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>249</v>
@@ -7117,7 +7117,7 @@
         <v>265</v>
       </c>
       <c r="G182" s="2">
-        <v>12.14</v>
+        <v>24</v>
       </c>
       <c r="H182" s="2">
         <v>0</v>
@@ -7134,22 +7134,18 @@
         <v>149</v>
       </c>
       <c r="B183" s="2">
-        <v>46033.34579861111</v>
+        <v>46033.34171296296</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D183" s="2">
-        <v>46033.66734953703</v>
-      </c>
-      <c r="E183" s="2" t="s">
-        <v>249</v>
-      </c>
+      <c r="D183" s="2"/>
+      <c r="E183" s="2"/>
       <c r="F183" s="2" t="s">
         <v>265</v>
       </c>
       <c r="G183" s="2">
-        <v>15.16</v>
+        <v>18</v>
       </c>
       <c r="H183" s="2">
         <v>0</v>
@@ -7166,13 +7162,13 @@
         <v>150</v>
       </c>
       <c r="B184" s="2">
-        <v>46033.32282407407</v>
+        <v>46033.33515046296</v>
       </c>
       <c r="C184" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D184" s="2">
-        <v>46033.68956018519</v>
+        <v>46033.6758912037</v>
       </c>
       <c r="E184" s="2" t="s">
         <v>249</v>
@@ -7198,13 +7194,13 @@
         <v>151</v>
       </c>
       <c r="B185" s="2">
-        <v>46033.33432870371</v>
+        <v>46033.34579861111</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D185" s="2">
-        <v>46033.6796412037</v>
+        <v>46033.66734953703</v>
       </c>
       <c r="E185" s="2" t="s">
         <v>249</v>
@@ -7213,7 +7209,7 @@
         <v>265</v>
       </c>
       <c r="G185" s="2">
-        <v>24</v>
+        <v>15.16</v>
       </c>
       <c r="H185" s="2">
         <v>0</v>
@@ -7230,22 +7226,18 @@
         <v>152</v>
       </c>
       <c r="B186" s="2">
-        <v>46033.32128472222</v>
+        <v>46033.32868055555</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D186" s="2">
-        <v>46033.64763888889</v>
-      </c>
-      <c r="E186" s="2" t="s">
-        <v>249</v>
-      </c>
+      <c r="D186" s="2"/>
+      <c r="E186" s="2"/>
       <c r="F186" s="2" t="s">
         <v>265</v>
       </c>
       <c r="G186" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H186" s="2">
         <v>0</v>
@@ -7262,18 +7254,22 @@
         <v>153</v>
       </c>
       <c r="B187" s="2">
-        <v>46033.34171296296</v>
+        <v>46033.33989583333</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D187" s="2"/>
-      <c r="E187" s="2"/>
+      <c r="D187" s="2">
+        <v>46033.6544212963</v>
+      </c>
+      <c r="E187" s="2" t="s">
+        <v>249</v>
+      </c>
       <c r="F187" s="2" t="s">
         <v>265</v>
       </c>
       <c r="G187" s="2">
-        <v>18</v>
+        <v>15.16</v>
       </c>
       <c r="H187" s="2">
         <v>0</v>
@@ -7290,13 +7286,13 @@
         <v>154</v>
       </c>
       <c r="B188" s="2">
-        <v>46033.33515046296</v>
+        <v>46033.32282407407</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D188" s="2">
-        <v>46033.6758912037</v>
+        <v>46033.68956018519</v>
       </c>
       <c r="E188" s="2" t="s">
         <v>249</v>
@@ -7322,13 +7318,13 @@
         <v>155</v>
       </c>
       <c r="B189" s="2">
-        <v>46033.33989583333</v>
+        <v>46033.3380787037</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D189" s="2">
-        <v>46033.6544212963</v>
+        <v>46033.6534375</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>249</v>
@@ -7337,7 +7333,7 @@
         <v>265</v>
       </c>
       <c r="G189" s="2">
-        <v>15.16</v>
+        <v>12.14</v>
       </c>
       <c r="H189" s="2">
         <v>0</v>
@@ -7354,18 +7350,22 @@
         <v>156</v>
       </c>
       <c r="B190" s="2">
-        <v>46033.32868055555</v>
+        <v>46033.3293287037</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D190" s="2"/>
-      <c r="E190" s="2"/>
+      <c r="D190" s="2">
+        <v>46033.67461805556</v>
+      </c>
+      <c r="E190" s="2" t="s">
+        <v>249</v>
+      </c>
       <c r="F190" s="2" t="s">
         <v>265</v>
       </c>
       <c r="G190" s="2">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H190" s="2">
         <v>0</v>
@@ -7382,13 +7382,13 @@
         <v>157</v>
       </c>
       <c r="B191" s="2">
-        <v>46033.3293287037</v>
+        <v>46033.32128472222</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D191" s="2">
-        <v>46033.67461805556</v>
+        <v>46033.64763888889</v>
       </c>
       <c r="E191" s="2" t="s">
         <v>249</v>
@@ -7397,7 +7397,7 @@
         <v>265</v>
       </c>
       <c r="G191" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H191" s="2">
         <v>0</v>
@@ -7446,13 +7446,13 @@
         <v>159</v>
       </c>
       <c r="B193" s="2">
-        <v>46033.31015046296</v>
+        <v>46033.49075231481</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D193" s="2">
-        <v>46033.65076388889</v>
+        <v>46033.83309027777</v>
       </c>
       <c r="E193" s="2" t="s">
         <v>249</v>
@@ -7461,7 +7461,7 @@
         <v>267</v>
       </c>
       <c r="G193" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H193" s="2">
         <v>0</v>
@@ -7478,13 +7478,13 @@
         <v>160</v>
       </c>
       <c r="B194" s="2">
-        <v>46033.49075231481</v>
+        <v>46033.28939814815</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D194" s="2">
-        <v>46033.83309027777</v>
+        <v>46033.49862268518</v>
       </c>
       <c r="E194" s="2" t="s">
         <v>249</v>
@@ -7493,7 +7493,7 @@
         <v>267</v>
       </c>
       <c r="G194" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H194" s="2">
         <v>0</v>
@@ -7510,13 +7510,13 @@
         <v>161</v>
       </c>
       <c r="B195" s="2">
-        <v>46033.28939814815</v>
+        <v>46033.3100462963</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D195" s="2">
-        <v>46033.49862268518</v>
+        <v>46033.65092592593</v>
       </c>
       <c r="E195" s="2" t="s">
         <v>249</v>
@@ -7525,7 +7525,7 @@
         <v>267</v>
       </c>
       <c r="G195" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H195" s="2">
         <v>0</v>
@@ -7542,13 +7542,13 @@
         <v>162</v>
       </c>
       <c r="B196" s="2">
-        <v>46033.3100462963</v>
+        <v>46033.31015046296</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D196" s="2">
-        <v>46033.65092592593</v>
+        <v>46033.65076388889</v>
       </c>
       <c r="E196" s="2" t="s">
         <v>249</v>
@@ -7557,7 +7557,7 @@
         <v>267</v>
       </c>
       <c r="G196" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H196" s="2">
         <v>0</v>
@@ -7577,19 +7577,19 @@
         <v>46033.33333333334</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D197" s="2">
         <v>46033.33333333334</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F197" s="2" t="s">
         <v>268</v>
       </c>
       <c r="G197" s="2">
-        <v>12.14</v>
+        <v>15.16</v>
       </c>
       <c r="H197" s="2">
         <v>8</v>
@@ -7702,22 +7702,18 @@
         <v>167</v>
       </c>
       <c r="B201" s="2">
-        <v>46033.37245370371</v>
+        <v>46033.34637731482</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D201" s="2">
-        <v>46033.73575231482</v>
-      </c>
-      <c r="E201" s="2" t="s">
-        <v>249</v>
-      </c>
+      <c r="D201" s="2"/>
+      <c r="E201" s="2"/>
       <c r="F201" s="2" t="s">
         <v>268</v>
       </c>
       <c r="G201" s="2">
-        <v>15.16</v>
+        <v>17</v>
       </c>
       <c r="H201" s="2">
         <v>0</v>
@@ -7734,13 +7730,13 @@
         <v>168</v>
       </c>
       <c r="B202" s="2">
-        <v>46033.58325231481</v>
+        <v>46033.57061342592</v>
       </c>
       <c r="C202" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D202" s="2">
-        <v>46033.85565972222</v>
+        <v>46033.87049768519</v>
       </c>
       <c r="E202" s="2" t="s">
         <v>249</v>
@@ -7749,7 +7745,7 @@
         <v>268</v>
       </c>
       <c r="G202" s="2">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H202" s="2">
         <v>0</v>
@@ -7766,13 +7762,13 @@
         <v>169</v>
       </c>
       <c r="B203" s="2">
-        <v>46033.58171296296</v>
+        <v>46033.32605324074</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D203" s="2">
-        <v>46033.86188657407</v>
+        <v>46033.58887731482</v>
       </c>
       <c r="E203" s="2" t="s">
         <v>249</v>
@@ -7781,7 +7777,7 @@
         <v>268</v>
       </c>
       <c r="G203" s="2">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="H203" s="2">
         <v>0</v>
@@ -7798,18 +7794,22 @@
         <v>170</v>
       </c>
       <c r="B204" s="2">
-        <v>46033.34637731482</v>
+        <v>46033.58325231481</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D204" s="2"/>
-      <c r="E204" s="2"/>
+      <c r="D204" s="2">
+        <v>46033.85565972222</v>
+      </c>
+      <c r="E204" s="2" t="s">
+        <v>249</v>
+      </c>
       <c r="F204" s="2" t="s">
         <v>268</v>
       </c>
       <c r="G204" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H204" s="2">
         <v>0</v>
@@ -7826,13 +7826,13 @@
         <v>171</v>
       </c>
       <c r="B205" s="2">
-        <v>46033.57061342592</v>
+        <v>46033.37245370371</v>
       </c>
       <c r="C205" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D205" s="2">
-        <v>46033.87049768519</v>
+        <v>46033.73575231482</v>
       </c>
       <c r="E205" s="2" t="s">
         <v>249</v>
@@ -7841,7 +7841,7 @@
         <v>268</v>
       </c>
       <c r="G205" s="2">
-        <v>23</v>
+        <v>15.16</v>
       </c>
       <c r="H205" s="2">
         <v>0</v>
@@ -7858,16 +7858,16 @@
         <v>172</v>
       </c>
       <c r="B206" s="2">
-        <v>46033.33333333334</v>
+        <v>46033.40175925926</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D206" s="2">
-        <v>46033.33333333334</v>
+        <v>46033.6912037037</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="F206" s="2" t="s">
         <v>268</v>
@@ -7876,7 +7876,7 @@
         <v>15.16</v>
       </c>
       <c r="H206" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I206" s="2">
         <v>0</v>
@@ -7890,13 +7890,13 @@
         <v>173</v>
       </c>
       <c r="B207" s="2">
-        <v>46033.40175925926</v>
+        <v>46033.58171296296</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D207" s="2">
-        <v>46033.6912037037</v>
+        <v>46033.86188657407</v>
       </c>
       <c r="E207" s="2" t="s">
         <v>249</v>
@@ -7905,7 +7905,7 @@
         <v>268</v>
       </c>
       <c r="G207" s="2">
-        <v>15.16</v>
+        <v>19</v>
       </c>
       <c r="H207" s="2">
         <v>0</v>
@@ -7954,25 +7954,25 @@
         <v>175</v>
       </c>
       <c r="B209" s="2">
-        <v>46033.32605324074</v>
+        <v>46033.33333333334</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D209" s="2">
-        <v>46033.58887731482</v>
+        <v>46033.33333333334</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="F209" s="2" t="s">
         <v>268</v>
       </c>
       <c r="G209" s="2">
-        <v>18.5</v>
+        <v>12.14</v>
       </c>
       <c r="H209" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I209" s="2">
         <v>0</v>
@@ -7986,13 +7986,13 @@
         <v>176</v>
       </c>
       <c r="B210" s="2">
-        <v>46033.3330787037</v>
+        <v>46033.37416666667</v>
       </c>
       <c r="C210" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D210" s="2">
-        <v>46033.67075231481</v>
+        <v>46033.68576388889</v>
       </c>
       <c r="E210" s="2" t="s">
         <v>249</v>
@@ -8001,7 +8001,7 @@
         <v>269</v>
       </c>
       <c r="G210" s="2">
-        <v>15.16</v>
+        <v>13</v>
       </c>
       <c r="H210" s="2">
         <v>0</v>
@@ -8018,13 +8018,13 @@
         <v>177</v>
       </c>
       <c r="B211" s="2">
-        <v>46033.33385416667</v>
+        <v>46033.32993055556</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D211" s="2">
-        <v>46033.67416666666</v>
+        <v>46033.69204861111</v>
       </c>
       <c r="E211" s="2" t="s">
         <v>249</v>
@@ -8033,7 +8033,7 @@
         <v>269</v>
       </c>
       <c r="G211" s="2">
-        <v>20.5</v>
+        <v>25</v>
       </c>
       <c r="H211" s="2">
         <v>0</v>
@@ -8050,13 +8050,13 @@
         <v>178</v>
       </c>
       <c r="B212" s="2">
-        <v>46033.57924768519</v>
+        <v>46033.3330787037</v>
       </c>
       <c r="C212" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D212" s="2">
-        <v>46033.93003472222</v>
+        <v>46033.67075231481</v>
       </c>
       <c r="E212" s="2" t="s">
         <v>249</v>
@@ -8065,7 +8065,7 @@
         <v>269</v>
       </c>
       <c r="G212" s="2">
-        <v>17</v>
+        <v>15.16</v>
       </c>
       <c r="H212" s="2">
         <v>0</v>
@@ -8082,13 +8082,13 @@
         <v>179</v>
       </c>
       <c r="B213" s="2">
-        <v>46033.45616898148</v>
+        <v>46033.33385416667</v>
       </c>
       <c r="C213" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D213" s="2">
-        <v>46033.81873842593</v>
+        <v>46033.67416666666</v>
       </c>
       <c r="E213" s="2" t="s">
         <v>249</v>
@@ -8097,7 +8097,7 @@
         <v>269</v>
       </c>
       <c r="G213" s="2">
-        <v>15.16</v>
+        <v>20.5</v>
       </c>
       <c r="H213" s="2">
         <v>0</v>
@@ -8114,13 +8114,13 @@
         <v>180</v>
       </c>
       <c r="B214" s="2">
-        <v>46033.57131944445</v>
+        <v>46033.57924768519</v>
       </c>
       <c r="C214" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D214" s="2">
-        <v>46033.93024305555</v>
+        <v>46033.93003472222</v>
       </c>
       <c r="E214" s="2" t="s">
         <v>249</v>
@@ -8129,7 +8129,7 @@
         <v>269</v>
       </c>
       <c r="G214" s="2">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H214" s="2">
         <v>0</v>
@@ -8146,13 +8146,13 @@
         <v>181</v>
       </c>
       <c r="B215" s="2">
-        <v>46033.31376157407</v>
+        <v>46033.45616898148</v>
       </c>
       <c r="C215" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D215" s="2">
-        <v>46033.67219907408</v>
+        <v>46033.81873842593</v>
       </c>
       <c r="E215" s="2" t="s">
         <v>249</v>
@@ -8178,13 +8178,13 @@
         <v>182</v>
       </c>
       <c r="B216" s="2">
-        <v>46033.40206018519</v>
+        <v>46033.57131944445</v>
       </c>
       <c r="C216" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D216" s="2">
-        <v>46033.67163194445</v>
+        <v>46033.93024305555</v>
       </c>
       <c r="E216" s="2" t="s">
         <v>249</v>
@@ -8193,7 +8193,7 @@
         <v>269</v>
       </c>
       <c r="G216" s="2">
-        <v>15.16</v>
+        <v>22</v>
       </c>
       <c r="H216" s="2">
         <v>0</v>
@@ -8210,13 +8210,13 @@
         <v>183</v>
       </c>
       <c r="B217" s="2">
-        <v>46033.33502314815</v>
+        <v>46033.31376157407</v>
       </c>
       <c r="C217" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D217" s="2">
-        <v>46033.6662037037</v>
+        <v>46033.67219907408</v>
       </c>
       <c r="E217" s="2" t="s">
         <v>249</v>
@@ -8225,7 +8225,7 @@
         <v>269</v>
       </c>
       <c r="G217" s="2">
-        <v>21</v>
+        <v>15.16</v>
       </c>
       <c r="H217" s="2">
         <v>0</v>
@@ -8242,13 +8242,13 @@
         <v>184</v>
       </c>
       <c r="B218" s="2">
-        <v>46033.37416666667</v>
+        <v>46033.40206018519</v>
       </c>
       <c r="C218" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D218" s="2">
-        <v>46033.68576388889</v>
+        <v>46033.67163194445</v>
       </c>
       <c r="E218" s="2" t="s">
         <v>249</v>
@@ -8257,7 +8257,7 @@
         <v>269</v>
       </c>
       <c r="G218" s="2">
-        <v>13</v>
+        <v>15.16</v>
       </c>
       <c r="H218" s="2">
         <v>0</v>
@@ -8274,13 +8274,13 @@
         <v>185</v>
       </c>
       <c r="B219" s="2">
-        <v>46033.38362268519</v>
+        <v>46033.33502314815</v>
       </c>
       <c r="C219" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D219" s="2">
-        <v>46033.65947916666</v>
+        <v>46033.6662037037</v>
       </c>
       <c r="E219" s="2" t="s">
         <v>249</v>
@@ -8289,7 +8289,7 @@
         <v>269</v>
       </c>
       <c r="G219" s="2">
-        <v>12.14</v>
+        <v>21</v>
       </c>
       <c r="H219" s="2">
         <v>0</v>
@@ -8306,13 +8306,13 @@
         <v>186</v>
       </c>
       <c r="B220" s="2">
-        <v>46033.39342592593</v>
+        <v>46033.57155092592</v>
       </c>
       <c r="C220" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D220" s="2">
-        <v>46033.58936342593</v>
+        <v>46033.93067129629</v>
       </c>
       <c r="E220" s="2" t="s">
         <v>249</v>
@@ -8321,7 +8321,7 @@
         <v>269</v>
       </c>
       <c r="G220" s="2">
-        <v>15.16</v>
+        <v>21</v>
       </c>
       <c r="H220" s="2">
         <v>0</v>
@@ -8338,13 +8338,13 @@
         <v>187</v>
       </c>
       <c r="B221" s="2">
-        <v>46033.33722222222</v>
+        <v>46033.63386574074</v>
       </c>
       <c r="C221" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D221" s="2">
-        <v>46033.68837962963</v>
+        <v>46033.63402777778</v>
       </c>
       <c r="E221" s="2" t="s">
         <v>249</v>
@@ -8353,7 +8353,7 @@
         <v>269</v>
       </c>
       <c r="G221" s="2">
-        <v>20</v>
+        <v>12.14</v>
       </c>
       <c r="H221" s="2">
         <v>0</v>
@@ -8370,13 +8370,13 @@
         <v>188</v>
       </c>
       <c r="B222" s="2">
-        <v>46033.63428240741</v>
+        <v>46033.33722222222</v>
       </c>
       <c r="C222" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D222" s="2">
-        <v>46033.89734953704</v>
+        <v>46033.68837962963</v>
       </c>
       <c r="E222" s="2" t="s">
         <v>249</v>
@@ -8402,13 +8402,13 @@
         <v>189</v>
       </c>
       <c r="B223" s="2">
-        <v>46033.30376157408</v>
+        <v>46033.39342592593</v>
       </c>
       <c r="C223" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D223" s="2">
-        <v>46033.55521990741</v>
+        <v>46033.58936342593</v>
       </c>
       <c r="E223" s="2" t="s">
         <v>249</v>
@@ -8417,7 +8417,7 @@
         <v>269</v>
       </c>
       <c r="G223" s="2">
-        <v>22</v>
+        <v>15.16</v>
       </c>
       <c r="H223" s="2">
         <v>0</v>
@@ -8434,13 +8434,13 @@
         <v>190</v>
       </c>
       <c r="B224" s="2">
-        <v>46033.62368055555</v>
+        <v>46033.38362268519</v>
       </c>
       <c r="C224" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D224" s="2">
-        <v>46033.74844907408</v>
+        <v>46033.65947916666</v>
       </c>
       <c r="E224" s="2" t="s">
         <v>249</v>
@@ -8449,7 +8449,7 @@
         <v>269</v>
       </c>
       <c r="G224" s="2">
-        <v>15.16</v>
+        <v>12.14</v>
       </c>
       <c r="H224" s="2">
         <v>0</v>
@@ -8498,13 +8498,13 @@
         <v>192</v>
       </c>
       <c r="B226" s="2">
-        <v>46033.57155092592</v>
+        <v>46033.62368055555</v>
       </c>
       <c r="C226" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D226" s="2">
-        <v>46033.93067129629</v>
+        <v>46033.74844907408</v>
       </c>
       <c r="E226" s="2" t="s">
         <v>249</v>
@@ -8513,7 +8513,7 @@
         <v>269</v>
       </c>
       <c r="G226" s="2">
-        <v>21</v>
+        <v>15.16</v>
       </c>
       <c r="H226" s="2">
         <v>0</v>
@@ -8530,13 +8530,13 @@
         <v>193</v>
       </c>
       <c r="B227" s="2">
-        <v>46033.32993055556</v>
+        <v>46033.30376157408</v>
       </c>
       <c r="C227" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D227" s="2">
-        <v>46033.69204861111</v>
+        <v>46033.55521990741</v>
       </c>
       <c r="E227" s="2" t="s">
         <v>249</v>
@@ -8545,7 +8545,7 @@
         <v>269</v>
       </c>
       <c r="G227" s="2">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H227" s="2">
         <v>0</v>
@@ -8559,16 +8559,16 @@
     </row>
     <row r="228" spans="1:10">
       <c r="A228" s="2" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="B228" s="2">
-        <v>46033.69251157407</v>
+        <v>46033.63428240741</v>
       </c>
       <c r="C228" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D228" s="2">
-        <v>46033.69262731481</v>
+        <v>46033.89734953704</v>
       </c>
       <c r="E228" s="2" t="s">
         <v>249</v>
@@ -8577,7 +8577,7 @@
         <v>269</v>
       </c>
       <c r="G228" s="2">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H228" s="2">
         <v>0</v>
@@ -8591,16 +8591,16 @@
     </row>
     <row r="229" spans="1:10">
       <c r="A229" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B229" s="2">
-        <v>46033.63386574074</v>
+        <v>46033.69251157407</v>
       </c>
       <c r="C229" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D229" s="2">
-        <v>46033.63402777778</v>
+        <v>46033.69262731481</v>
       </c>
       <c r="E229" s="2" t="s">
         <v>249</v>
@@ -8609,7 +8609,7 @@
         <v>269</v>
       </c>
       <c r="G229" s="2">
-        <v>12.14</v>
+        <v>13</v>
       </c>
       <c r="H229" s="2">
         <v>0</v>
@@ -8626,13 +8626,13 @@
         <v>195</v>
       </c>
       <c r="B230" s="2">
-        <v>46033.28596064815</v>
+        <v>46033.37269675926</v>
       </c>
       <c r="C230" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D230" s="2">
-        <v>46033.64358796296</v>
+        <v>46033.70159722222</v>
       </c>
       <c r="E230" s="2" t="s">
         <v>249</v>
@@ -8658,13 +8658,13 @@
         <v>196</v>
       </c>
       <c r="B231" s="2">
-        <v>46033.3331712963</v>
+        <v>46033.28596064815</v>
       </c>
       <c r="C231" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D231" s="2">
-        <v>46033.66675925926</v>
+        <v>46033.64358796296</v>
       </c>
       <c r="E231" s="2" t="s">
         <v>249</v>
@@ -8690,13 +8690,13 @@
         <v>197</v>
       </c>
       <c r="B232" s="2">
-        <v>46033.37269675926</v>
+        <v>46033.3331712963</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D232" s="2">
-        <v>46033.70159722222</v>
+        <v>46033.66675925926</v>
       </c>
       <c r="E232" s="2" t="s">
         <v>249</v>
@@ -8722,22 +8722,18 @@
         <v>198</v>
       </c>
       <c r="B233" s="2">
-        <v>46033.43796296296</v>
+        <v>46033.9489699074</v>
       </c>
       <c r="C233" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D233" s="2">
-        <v>46033.75238425926</v>
-      </c>
-      <c r="E233" s="2" t="s">
-        <v>249</v>
-      </c>
+      <c r="D233" s="2"/>
+      <c r="E233" s="2"/>
       <c r="F233" s="2" t="s">
         <v>271</v>
       </c>
       <c r="G233" s="2">
-        <v>26.1</v>
+        <v>19.34</v>
       </c>
       <c r="H233" s="2">
         <v>0</v>
@@ -8754,18 +8750,22 @@
         <v>199</v>
       </c>
       <c r="B234" s="2">
-        <v>46033.9489699074</v>
+        <v>46033.43796296296</v>
       </c>
       <c r="C234" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D234" s="2"/>
-      <c r="E234" s="2"/>
+      <c r="D234" s="2">
+        <v>46033.75238425926</v>
+      </c>
+      <c r="E234" s="2" t="s">
+        <v>249</v>
+      </c>
       <c r="F234" s="2" t="s">
         <v>271</v>
       </c>
       <c r="G234" s="2">
-        <v>19.34</v>
+        <v>26.1</v>
       </c>
       <c r="H234" s="2">
         <v>0</v>
@@ -8814,13 +8814,13 @@
         <v>201</v>
       </c>
       <c r="B236" s="2">
-        <v>46033.67038194444</v>
+        <v>46033.49270833333</v>
       </c>
       <c r="C236" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D236" s="2">
-        <v>46033.9291087963</v>
+        <v>46033.81324074074</v>
       </c>
       <c r="E236" s="2" t="s">
         <v>249</v>
@@ -8829,7 +8829,7 @@
         <v>271</v>
       </c>
       <c r="G236" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H236" s="2">
         <v>0</v>
@@ -8846,13 +8846,13 @@
         <v>202</v>
       </c>
       <c r="B237" s="2">
-        <v>46033.49270833333</v>
+        <v>46033.4509375</v>
       </c>
       <c r="C237" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D237" s="2">
-        <v>46033.81324074074</v>
+        <v>46033.9565625</v>
       </c>
       <c r="E237" s="2" t="s">
         <v>249</v>
@@ -8861,7 +8861,7 @@
         <v>271</v>
       </c>
       <c r="G237" s="2">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="H237" s="2">
         <v>0</v>
@@ -8878,13 +8878,13 @@
         <v>203</v>
       </c>
       <c r="B238" s="2">
-        <v>46033.4509375</v>
+        <v>46033.67038194444</v>
       </c>
       <c r="C238" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D238" s="2">
-        <v>46033.9565625</v>
+        <v>46033.9291087963</v>
       </c>
       <c r="E238" s="2" t="s">
         <v>249</v>
@@ -8893,7 +8893,7 @@
         <v>271</v>
       </c>
       <c r="G238" s="2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="H238" s="2">
         <v>0</v>
@@ -8910,13 +8910,13 @@
         <v>204</v>
       </c>
       <c r="B239" s="2">
-        <v>46033.40850694444</v>
+        <v>46033.31241898148</v>
       </c>
       <c r="C239" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D239" s="2">
-        <v>46033.68403935185</v>
+        <v>46033.64420138889</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>249</v>
@@ -8925,7 +8925,7 @@
         <v>272</v>
       </c>
       <c r="G239" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H239" s="2">
         <v>0</v>
@@ -8942,13 +8942,13 @@
         <v>205</v>
       </c>
       <c r="B240" s="2">
-        <v>46033.64729166667</v>
+        <v>46033.40850694444</v>
       </c>
       <c r="C240" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D240" s="2">
-        <v>46033.92023148148</v>
+        <v>46033.68403935185</v>
       </c>
       <c r="E240" s="2" t="s">
         <v>249</v>
@@ -8957,7 +8957,7 @@
         <v>272</v>
       </c>
       <c r="G240" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H240" s="2">
         <v>0</v>
@@ -8974,13 +8974,13 @@
         <v>206</v>
       </c>
       <c r="B241" s="2">
-        <v>46033.31241898148</v>
+        <v>46033.64729166667</v>
       </c>
       <c r="C241" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D241" s="2">
-        <v>46033.64420138889</v>
+        <v>46033.92023148148</v>
       </c>
       <c r="E241" s="2" t="s">
         <v>249</v>
@@ -9038,13 +9038,13 @@
         <v>208</v>
       </c>
       <c r="B243" s="2">
-        <v>46033.34341435185</v>
+        <v>46033.34543981482</v>
       </c>
       <c r="C243" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D243" s="2">
-        <v>46033.67523148148</v>
+        <v>46033.67578703703</v>
       </c>
       <c r="E243" s="2" t="s">
         <v>249</v>
@@ -9070,13 +9070,13 @@
         <v>209</v>
       </c>
       <c r="B244" s="2">
-        <v>46033.32564814815</v>
+        <v>46033.34341435185</v>
       </c>
       <c r="C244" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D244" s="2">
-        <v>46033.74166666667</v>
+        <v>46033.67523148148</v>
       </c>
       <c r="E244" s="2" t="s">
         <v>249</v>
@@ -9085,7 +9085,7 @@
         <v>274</v>
       </c>
       <c r="G244" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H244" s="2">
         <v>0</v>
@@ -9102,13 +9102,13 @@
         <v>210</v>
       </c>
       <c r="B245" s="2">
-        <v>46033.34543981482</v>
+        <v>46033.32564814815</v>
       </c>
       <c r="C245" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D245" s="2">
-        <v>46033.67578703703</v>
+        <v>46033.74166666667</v>
       </c>
       <c r="E245" s="2" t="s">
         <v>249</v>
@@ -9117,7 +9117,7 @@
         <v>274</v>
       </c>
       <c r="G245" s="2">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H245" s="2">
         <v>0</v>
@@ -9137,13 +9137,13 @@
         <v>46033.5</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D246" s="2">
         <v>46033.5</v>
       </c>
       <c r="E246" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F246" s="2" t="s">
         <v>275</v>
@@ -9166,13 +9166,13 @@
         <v>212</v>
       </c>
       <c r="B247" s="2">
-        <v>46033.54976851852</v>
+        <v>46033.54113425926</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D247" s="2">
-        <v>46033.67944444445</v>
+        <v>46033.70318287037</v>
       </c>
       <c r="E247" s="2" t="s">
         <v>249</v>
@@ -9181,7 +9181,7 @@
         <v>275</v>
       </c>
       <c r="G247" s="2">
-        <v>25.34</v>
+        <v>22.88</v>
       </c>
       <c r="H247" s="2">
         <v>0</v>
@@ -9198,13 +9198,13 @@
         <v>212</v>
       </c>
       <c r="B248" s="2">
-        <v>46033.3049537037</v>
+        <v>46033.33814814815</v>
       </c>
       <c r="C248" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D248" s="2">
-        <v>46033.52438657408</v>
+        <v>46033.52398148148</v>
       </c>
       <c r="E248" s="2" t="s">
         <v>250</v>
@@ -9213,7 +9213,7 @@
         <v>275</v>
       </c>
       <c r="G248" s="2">
-        <v>25.34</v>
+        <v>22.88</v>
       </c>
       <c r="H248" s="2">
         <v>0</v>
@@ -9230,13 +9230,13 @@
         <v>213</v>
       </c>
       <c r="B249" s="2">
-        <v>46033.54092592592</v>
+        <v>46033.54976851852</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D249" s="2">
-        <v>46033.68600694444</v>
+        <v>46033.67944444445</v>
       </c>
       <c r="E249" s="2" t="s">
         <v>249</v>
@@ -9245,7 +9245,7 @@
         <v>275</v>
       </c>
       <c r="G249" s="2">
-        <v>20</v>
+        <v>25.34</v>
       </c>
       <c r="H249" s="2">
         <v>0</v>
@@ -9259,28 +9259,28 @@
     </row>
     <row r="250" spans="1:10">
       <c r="A250" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B250" s="2">
-        <v>46033.33259259259</v>
+        <v>46033.5</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D250" s="2">
-        <v>46033.51690972222</v>
+        <v>46033.5</v>
       </c>
       <c r="E250" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="F250" s="2" t="s">
         <v>275</v>
       </c>
       <c r="G250" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H250" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I250" s="2">
         <v>0</v>
@@ -9294,13 +9294,13 @@
         <v>214</v>
       </c>
       <c r="B251" s="2">
-        <v>46033.34391203704</v>
+        <v>46033.54092592592</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D251" s="2">
-        <v>46033.51189814815</v>
+        <v>46033.68600694444</v>
       </c>
       <c r="E251" s="2" t="s">
         <v>249</v>
@@ -9309,7 +9309,7 @@
         <v>275</v>
       </c>
       <c r="G251" s="2">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="H251" s="2">
         <v>0</v>
@@ -9323,25 +9323,25 @@
     </row>
     <row r="252" spans="1:10">
       <c r="A252" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B252" s="2">
-        <v>46033.59255787037</v>
+        <v>46033.33259259259</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D252" s="2">
-        <v>46033.69297453704</v>
+        <v>46033.51690972222</v>
       </c>
       <c r="E252" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F252" s="2" t="s">
         <v>275</v>
       </c>
       <c r="G252" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H252" s="2">
         <v>0</v>
@@ -9355,16 +9355,16 @@
     </row>
     <row r="253" spans="1:10">
       <c r="A253" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B253" s="2">
-        <v>46033.33241898148</v>
+        <v>46033.31115740741</v>
       </c>
       <c r="C253" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D253" s="2">
-        <v>46033.55484953704</v>
+        <v>46033.4733449074</v>
       </c>
       <c r="E253" s="2" t="s">
         <v>249</v>
@@ -9373,7 +9373,7 @@
         <v>275</v>
       </c>
       <c r="G253" s="2">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="H253" s="2">
         <v>0</v>
@@ -9387,25 +9387,25 @@
     </row>
     <row r="254" spans="1:10">
       <c r="A254" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B254" s="2">
-        <v>46033.54262731481</v>
+        <v>46033.3049537037</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D254" s="2">
-        <v>46033.67577546297</v>
+        <v>46033.52438657408</v>
       </c>
       <c r="E254" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F254" s="2" t="s">
         <v>275</v>
       </c>
       <c r="G254" s="2">
-        <v>17.5</v>
+        <v>25.34</v>
       </c>
       <c r="H254" s="2">
         <v>0</v>
@@ -9419,25 +9419,25 @@
     </row>
     <row r="255" spans="1:10">
       <c r="A255" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B255" s="2">
-        <v>46033.32591435185</v>
+        <v>46033.54244212963</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D255" s="2">
-        <v>46033.51091435185</v>
+        <v>46033.67777777778</v>
       </c>
       <c r="E255" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F255" s="2" t="s">
         <v>275</v>
       </c>
       <c r="G255" s="2">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="H255" s="2">
         <v>0</v>
@@ -9451,16 +9451,16 @@
     </row>
     <row r="256" spans="1:10">
       <c r="A256" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B256" s="2">
-        <v>46033.33814814815</v>
+        <v>46033.3280787037</v>
       </c>
       <c r="C256" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D256" s="2">
-        <v>46033.52398148148</v>
+        <v>46033.50467592593</v>
       </c>
       <c r="E256" s="2" t="s">
         <v>250</v>
@@ -9469,7 +9469,7 @@
         <v>275</v>
       </c>
       <c r="G256" s="2">
-        <v>22.88</v>
+        <v>18.5</v>
       </c>
       <c r="H256" s="2">
         <v>0</v>
@@ -9483,7 +9483,7 @@
     </row>
     <row r="257" spans="1:10">
       <c r="A257" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B257" s="2">
         <v>46033.33171296296</v>
@@ -9515,28 +9515,28 @@
     </row>
     <row r="258" spans="1:10">
       <c r="A258" s="2" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="B258" s="2">
-        <v>46033.5</v>
+        <v>46033.32784722222</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D258" s="2">
-        <v>46033.5</v>
+        <v>46033.55438657408</v>
       </c>
       <c r="E258" s="2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="F258" s="2" t="s">
         <v>275</v>
       </c>
       <c r="G258" s="2">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="H258" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I258" s="2">
         <v>0</v>
@@ -9547,16 +9547,16 @@
     </row>
     <row r="259" spans="1:10">
       <c r="A259" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B259" s="2">
-        <v>46033.54113425926</v>
+        <v>46033.32774305555</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D259" s="2">
-        <v>46033.70318287037</v>
+        <v>46033.55461805555</v>
       </c>
       <c r="E259" s="2" t="s">
         <v>249</v>
@@ -9565,7 +9565,7 @@
         <v>275</v>
       </c>
       <c r="G259" s="2">
-        <v>22.88</v>
+        <v>18.5</v>
       </c>
       <c r="H259" s="2">
         <v>0</v>
@@ -9579,16 +9579,16 @@
     </row>
     <row r="260" spans="1:10">
       <c r="A260" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B260" s="2">
-        <v>46033.54244212963</v>
+        <v>46033.31189814815</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D260" s="2">
-        <v>46033.67777777778</v>
+        <v>46033.50165509259</v>
       </c>
       <c r="E260" s="2" t="s">
         <v>249</v>
@@ -9597,7 +9597,7 @@
         <v>275</v>
       </c>
       <c r="G260" s="2">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="H260" s="2">
         <v>0</v>
@@ -9611,19 +9611,19 @@
     </row>
     <row r="261" spans="1:10">
       <c r="A261" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B261" s="2">
-        <v>46033.32988425926</v>
+        <v>46033.48734953703</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D261" s="2">
-        <v>46033.46569444444</v>
+        <v>46033.69334490741</v>
       </c>
       <c r="E261" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F261" s="2" t="s">
         <v>275</v>
@@ -9643,16 +9643,16 @@
     </row>
     <row r="262" spans="1:10">
       <c r="A262" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B262" s="2">
-        <v>46033.48734953703</v>
+        <v>46033.59255787037</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D262" s="2">
-        <v>46033.69334490741</v>
+        <v>46033.69297453704</v>
       </c>
       <c r="E262" s="2" t="s">
         <v>249</v>
@@ -9661,7 +9661,7 @@
         <v>275</v>
       </c>
       <c r="G262" s="2">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="H262" s="2">
         <v>0</v>
@@ -9675,16 +9675,16 @@
     </row>
     <row r="263" spans="1:10">
       <c r="A263" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B263" s="2">
-        <v>46033.31189814815</v>
+        <v>46033.34391203704</v>
       </c>
       <c r="C263" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D263" s="2">
-        <v>46033.50165509259</v>
+        <v>46033.51189814815</v>
       </c>
       <c r="E263" s="2" t="s">
         <v>249</v>
@@ -9693,7 +9693,7 @@
         <v>275</v>
       </c>
       <c r="G263" s="2">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="H263" s="2">
         <v>0</v>
@@ -9707,16 +9707,16 @@
     </row>
     <row r="264" spans="1:10">
       <c r="A264" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B264" s="2">
-        <v>46033.32774305555</v>
+        <v>46033.33241898148</v>
       </c>
       <c r="C264" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D264" s="2">
-        <v>46033.55461805555</v>
+        <v>46033.55484953704</v>
       </c>
       <c r="E264" s="2" t="s">
         <v>249</v>
@@ -9725,7 +9725,7 @@
         <v>275</v>
       </c>
       <c r="G264" s="2">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="H264" s="2">
         <v>0</v>
@@ -9739,16 +9739,16 @@
     </row>
     <row r="265" spans="1:10">
       <c r="A265" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B265" s="2">
-        <v>46033.32784722222</v>
+        <v>46033.54262731481</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D265" s="2">
-        <v>46033.55438657408</v>
+        <v>46033.67577546297</v>
       </c>
       <c r="E265" s="2" t="s">
         <v>249</v>
@@ -9774,16 +9774,16 @@
         <v>224</v>
       </c>
       <c r="B266" s="2">
-        <v>46033.31115740741</v>
+        <v>46033.32591435185</v>
       </c>
       <c r="C266" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D266" s="2">
-        <v>46033.4733449074</v>
+        <v>46033.51091435185</v>
       </c>
       <c r="E266" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F266" s="2" t="s">
         <v>275</v>
@@ -9803,16 +9803,16 @@
     </row>
     <row r="267" spans="1:10">
       <c r="A267" s="2" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="B267" s="2">
-        <v>46033.3280787037</v>
+        <v>46033.32814814815</v>
       </c>
       <c r="C267" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D267" s="2">
-        <v>46033.50467592593</v>
+        <v>46033.50475694444</v>
       </c>
       <c r="E267" s="2" t="s">
         <v>250</v>
@@ -9835,16 +9835,16 @@
     </row>
     <row r="268" spans="1:10">
       <c r="A268" s="2" t="s">
-        <v>5</v>
+        <v>221</v>
       </c>
       <c r="B268" s="2">
-        <v>46033.32814814815</v>
+        <v>46033.32988425926</v>
       </c>
       <c r="C268" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D268" s="2">
-        <v>46033.50475694444</v>
+        <v>46033.46569444444</v>
       </c>
       <c r="E268" s="2" t="s">
         <v>250</v>
@@ -9870,13 +9870,13 @@
         <v>225</v>
       </c>
       <c r="B269" s="2">
-        <v>46033.54883101852</v>
+        <v>46033.50545138889</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D269" s="2">
-        <v>46033.70300925926</v>
+        <v>46033.76792824074</v>
       </c>
       <c r="E269" s="2" t="s">
         <v>249</v>
@@ -9885,7 +9885,7 @@
         <v>276</v>
       </c>
       <c r="G269" s="2">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="H269" s="2">
         <v>0</v>
@@ -9899,25 +9899,25 @@
     </row>
     <row r="270" spans="1:10">
       <c r="A270" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B270" s="2">
-        <v>46033.33278935185</v>
+        <v>46033.50516203704</v>
       </c>
       <c r="C270" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D270" s="2">
-        <v>46033.52724537037</v>
+        <v>46033.71202546296</v>
       </c>
       <c r="E270" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F270" s="2" t="s">
         <v>276</v>
       </c>
       <c r="G270" s="2">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="H270" s="2">
         <v>0</v>
@@ -9931,7 +9931,7 @@
     </row>
     <row r="271" spans="1:10">
       <c r="A271" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B271" s="2">
         <v>46033.59417824074</v>
@@ -9963,7 +9963,7 @@
     </row>
     <row r="272" spans="1:10">
       <c r="A272" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B272" s="2">
         <v>46033.40284722222</v>
@@ -9995,25 +9995,25 @@
     </row>
     <row r="273" spans="1:10">
       <c r="A273" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B273" s="2">
-        <v>46033.46875</v>
+        <v>46033.46974537037</v>
       </c>
       <c r="C273" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D273" s="2">
-        <v>46033.6875</v>
+        <v>46033.72094907407</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F273" s="2" t="s">
         <v>276</v>
       </c>
       <c r="G273" s="2">
-        <v>25</v>
+        <v>17.5</v>
       </c>
       <c r="H273" s="2">
         <v>0</v>
@@ -10027,13 +10027,13 @@
     </row>
     <row r="274" spans="1:10">
       <c r="A274" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B274" s="2">
         <v>46033.70833333334</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D274" s="2">
         <v>46033.7625</v>
@@ -10059,25 +10059,25 @@
     </row>
     <row r="275" spans="1:10">
       <c r="A275" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B275" s="2">
-        <v>46033.46974537037</v>
+        <v>46033.46875</v>
       </c>
       <c r="C275" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D275" s="2">
-        <v>46033.72094907407</v>
+        <v>46033.6875</v>
       </c>
       <c r="E275" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F275" s="2" t="s">
         <v>276</v>
       </c>
       <c r="G275" s="2">
-        <v>17.5</v>
+        <v>25</v>
       </c>
       <c r="H275" s="2">
         <v>0</v>
@@ -10091,16 +10091,16 @@
     </row>
     <row r="276" spans="1:10">
       <c r="A276" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B276" s="2">
-        <v>46033.50516203704</v>
+        <v>46033.54883101852</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D276" s="2">
-        <v>46033.71202546296</v>
+        <v>46033.70300925926</v>
       </c>
       <c r="E276" s="2" t="s">
         <v>249</v>
@@ -10109,7 +10109,7 @@
         <v>276</v>
       </c>
       <c r="G276" s="2">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="H276" s="2">
         <v>0</v>
@@ -10123,19 +10123,19 @@
     </row>
     <row r="277" spans="1:10">
       <c r="A277" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B277" s="2">
-        <v>46033.48019675926</v>
+        <v>46033.27134259259</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D277" s="2">
-        <v>46033.76744212963</v>
+        <v>46033.45408564815</v>
       </c>
       <c r="E277" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F277" s="2" t="s">
         <v>276</v>
@@ -10158,13 +10158,13 @@
         <v>231</v>
       </c>
       <c r="B278" s="2">
-        <v>46033.31259259259</v>
+        <v>46033.48019675926</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D278" s="2">
-        <v>46033.55253472222</v>
+        <v>46033.76744212963</v>
       </c>
       <c r="E278" s="2" t="s">
         <v>249</v>
@@ -10173,7 +10173,7 @@
         <v>276</v>
       </c>
       <c r="G278" s="2">
-        <v>25.5</v>
+        <v>26</v>
       </c>
       <c r="H278" s="2">
         <v>0</v>
@@ -10190,22 +10190,22 @@
         <v>232</v>
       </c>
       <c r="B279" s="2">
-        <v>46033.33328703704</v>
+        <v>46033.56418981482</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D279" s="2">
-        <v>46033.48788194444</v>
+        <v>46033.71486111111</v>
       </c>
       <c r="E279" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F279" s="2" t="s">
         <v>276</v>
       </c>
       <c r="G279" s="2">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="H279" s="2">
         <v>0</v>
@@ -10219,16 +10219,16 @@
     </row>
     <row r="280" spans="1:10">
       <c r="A280" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B280" s="2">
-        <v>46033.27134259259</v>
+        <v>46033.28068287037</v>
       </c>
       <c r="C280" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D280" s="2">
-        <v>46033.45408564815</v>
+        <v>46033.54337962963</v>
       </c>
       <c r="E280" s="2" t="s">
         <v>250</v>
@@ -10237,7 +10237,7 @@
         <v>276</v>
       </c>
       <c r="G280" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H280" s="2">
         <v>0</v>
@@ -10254,13 +10254,13 @@
         <v>233</v>
       </c>
       <c r="B281" s="2">
-        <v>46033.56418981482</v>
+        <v>46033.31259259259</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D281" s="2">
-        <v>46033.71486111111</v>
+        <v>46033.55253472222</v>
       </c>
       <c r="E281" s="2" t="s">
         <v>249</v>
@@ -10269,7 +10269,7 @@
         <v>276</v>
       </c>
       <c r="G281" s="2">
-        <v>22</v>
+        <v>25.5</v>
       </c>
       <c r="H281" s="2">
         <v>0</v>
@@ -10283,16 +10283,16 @@
     </row>
     <row r="282" spans="1:10">
       <c r="A282" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B282" s="2">
-        <v>46033.28068287037</v>
+        <v>46033.33328703704</v>
       </c>
       <c r="C282" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D282" s="2">
-        <v>46033.54337962963</v>
+        <v>46033.48788194444</v>
       </c>
       <c r="E282" s="2" t="s">
         <v>250</v>
@@ -10301,7 +10301,7 @@
         <v>276</v>
       </c>
       <c r="G282" s="2">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="H282" s="2">
         <v>0</v>
@@ -10315,19 +10315,19 @@
     </row>
     <row r="283" spans="1:10">
       <c r="A283" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B283" s="2">
-        <v>46033.51193287037</v>
+        <v>46033.33278935185</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D283" s="2">
-        <v>46033.76349537037</v>
+        <v>46033.52724537037</v>
       </c>
       <c r="E283" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F283" s="2" t="s">
         <v>276</v>
@@ -10350,13 +10350,13 @@
         <v>234</v>
       </c>
       <c r="B284" s="2">
-        <v>46033.50545138889</v>
+        <v>46033.51193287037</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D284" s="2">
-        <v>46033.76792824074</v>
+        <v>46033.76349537037</v>
       </c>
       <c r="E284" s="2" t="s">
         <v>249</v>
@@ -10365,7 +10365,7 @@
         <v>276</v>
       </c>
       <c r="G284" s="2">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="H284" s="2">
         <v>0</v>
@@ -10481,13 +10481,13 @@
         <v>46033.33333333334</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D288" s="2">
         <v>46033.33333333334</v>
       </c>
       <c r="E288" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F288" s="2" t="s">
         <v>279</v>
@@ -10534,7 +10534,7 @@
         <v>0</v>
       </c>
       <c r="J289" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="290" spans="1:10">
@@ -10547,8 +10547,12 @@
       <c r="C290" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D290" s="2"/>
-      <c r="E290" s="2"/>
+      <c r="D290" s="2">
+        <v>46033.6875</v>
+      </c>
+      <c r="E290" s="2" t="s">
+        <v>249</v>
+      </c>
       <c r="F290" s="2" t="s">
         <v>280</v>
       </c>
@@ -10562,7 +10566,7 @@
         <v>0</v>
       </c>
       <c r="J290" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="291" spans="1:10">
